--- a/Format Debugging dan Pengujian.xlsx
+++ b/Format Debugging dan Pengujian.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\peminjaman_buku\debug_&amp;_pengujian_webPeminjamanBuku\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4663CA91-DAE2-4F0E-9AD8-19FE4C02F56D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3696180D-755C-4A6D-9B46-E6DEB69BFDE4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="141">
   <si>
     <t xml:space="preserve">NIS : </t>
   </si>
@@ -294,13 +294,171 @@
   </si>
   <si>
     <t>Status peminjaman berubah, transaksi ditutup</t>
+  </si>
+  <si>
+    <t>Nama Lengkap : Zainab Putri Ramadhani</t>
+  </si>
+  <si>
+    <t>Selesai</t>
+  </si>
+  <si>
+    <t>Git belum terinstal sehingga tidak dapat membuat atau mengelola repository.</t>
+  </si>
+  <si>
+    <t>Menjalankan perintah git init, namun sistem tidak mengenali perintah tersebut.</t>
+  </si>
+  <si>
+    <t>Konfigurasi Sistem (Instalasi Git).</t>
+  </si>
+  <si>
+    <t>Mengunduh dan menginstal Git, kemudian melakukan konfigurasi awal agar dapat digunakan.</t>
+  </si>
+  <si>
+    <t>Implementasi Login, Register, dan Dashboard (Admin &amp; Anggota)</t>
+  </si>
+  <si>
+    <t>Terjadi kesalahan path saat proses login menuju dashboard (admin/anggota), serta beberapa navigasi belum memiliki halaman sehingga menampilkan error not found.</t>
+  </si>
+  <si>
+    <t>Login berhasil, namun redirect ke dashboard gagal karena path tidak sesuai.</t>
+  </si>
+  <si>
+    <t>Memperbaiki path/redirect pada proses login sesuai role pengguna</t>
+  </si>
+  <si>
+    <t>Pengembangan Role Login, Fitur Pencarian, dan Daftar Buku</t>
+  </si>
+  <si>
+    <t>Terjadi kesalahan pada pengelolaan role pengguna, di mana semua pengguna yang bukan admin otomatis diarahkan ke dashboard anggota, meskipun role tidak sesuai (misalnya bukan “anggota”).</t>
+  </si>
+  <si>
+    <t>Melakukan registrasi dengan role selain admin (atau input role tidak valid), kemudian login. Sistem tetap mengarahkan pengguna ke dashboard anggota karena kondisi hanya memeriksa role admin, sementara selain itu dianggap anggota.</t>
+  </si>
+  <si>
+    <t>Memperbaiki logika validasi role saat registrasi dan login, dengan membatasi role hanya pada nilai yang valid (admin dan anggota), serta menyesuaikan proses redirect berdasarkan role yang benar.</t>
+  </si>
+  <si>
+    <t>Fitur filter kategori pada halaman dashboard anggota sebelumnya tidak berfungsi sehingga data buku tidak terfilter sesuai kategori yang dipilih.</t>
+  </si>
+  <si>
+    <t>Memilih kategori pada dropdown filter, namun data buku yang ditampilkan tidak berubah karena parameter kategori belum diproses dengan benar pada query database.</t>
+  </si>
+  <si>
+    <t>Menambahkan pengolahan parameter GET pada filter kategori dan menyesuaikan query database agar data buku dapat difilter berdasarkan kategori yang dipilih, serta menambahkan tabel kategori pada database.</t>
+  </si>
+  <si>
+    <t>Pengembangan Halaman Pinjam dan Fitur Filter Kategori</t>
+  </si>
+  <si>
+    <t>Pengembangan Halaman Pengembalian Buku (Admin) dan Perbaikan Validasi Peminjaman</t>
+  </si>
+  <si>
+    <t>Terjadi error saat melakukan peminjaman dengan jumlah melebihi stok buku yang tersedia, sehingga sistem tidak memberikan validasi yang sesuai.</t>
+  </si>
+  <si>
+    <t>Memasukkan jumlah peminjaman lebih besar dari stok (misalnya stok 60, input 61), kemudian sistem tetap memproses tanpa validasi atau menimbulkan error karena tidak ada pengecekan batas stok.</t>
+  </si>
+  <si>
+    <t>Menambahkan validasi pada proses peminjaman untuk membatasi jumlah pinjam agar tidak melebihi stok yang tersedia, serta menampilkan pesan peringatan jika jumlah melebihi stok.</t>
+  </si>
+  <si>
+    <t>Pengembangan Halaman Riwayat Pengembalian dan Fitur Manajemen Data</t>
+  </si>
+  <si>
+    <t>Data riwayat pengembalian yang telah dihapus atau di-clear masih muncul kembali setelah melakukan reset, sehingga tidak terhapus secara permanen dari halaman.</t>
+  </si>
+  <si>
+    <t>Melakukan clear semua data atau menghapus data, kemudian menekan tombol reset. Data kembali muncul karena hanya disembunyikan menggunakan session dan tidak dihapus dari database.</t>
+  </si>
+  <si>
+    <t>Memperbaiki mekanisme penghapusan data dengan memastikan data benar-benar dihapus atau difilter langsung dari database, bukan hanya disimpan dalam session.</t>
+  </si>
+  <si>
+    <t>Pengembangan Halaman Peminjaman (Frontend)</t>
+  </si>
+  <si>
+    <t>Pengembangan Halaman Profil, Histori, dan Logout pada menu dropdown Lainnya</t>
+  </si>
+  <si>
+    <t>Tombol Edit Profil tidak berubah menjadi Tutup Form saat form edit ditampilkan, meskipun form sudah berhasil muncul.</t>
+  </si>
+  <si>
+    <t>Menekan tombol Edit Profil, form edit muncul namun teks tombol tetap menampilkan Edit Profil karena kondisi tampilan tombol tidak sinkron dengan state form.</t>
+  </si>
+  <si>
+    <t>Memperbaiki logika tampilan tombol dengan memastikan kondisi toggle antara Edit Profil dan Tutup Form berjalan dengan benar, serta menyesuaikan struktur elemen agar tidak terjadi konflik tampilan.</t>
+  </si>
+  <si>
+    <t>Kelola Data Buku (Upload Gambar)</t>
+  </si>
+  <si>
+    <t>Perubahan sistem upload gambar dari manual ke otomatis menyebabkan potensi ketidaksesuaian antara file di folder dan data di database, terutama pada data lama</t>
+  </si>
+  <si>
+    <t>1. Data buku lama menggunakan upload manual (file dipindah ke assets/gambar secara manual)
+2. Sistem baru menggunakan upload otomatis dari form
+3. Beberapa file lama tidak terdeteksi jika hanya mengandalkan path DB</t>
+  </si>
+  <si>
+    <t>Menyeragamkan struktur penyimpanan gambar di assets/gambar, memastikan nama file di database sesuai dengan file fisik, serta menambahkan validasi file_exists() untuk menjaga kompatibilitas data lama dan baru (konsep kotak hitam)</t>
+  </si>
+  <si>
+    <t>Kelola Anggota &amp; Transaksi (Search &amp; Filter)</t>
+  </si>
+  <si>
+    <t>Nilai input pencarian hilang ketika user menekan tombol cari atau berpindah kategori filter, sehingga user harus mengetik ulang keyword pencarian</t>
+  </si>
+  <si>
+    <t>1. User mengisi keyword pencarian buku
+2. Menekan tombol cari atau memilih kategori filter
+3. Halaman reload dan input search kembali kosong</t>
+  </si>
+  <si>
+    <t>Menjaga state keyword dengan menyimpan nilai dari $_POST/$_GET ke variabel $keyword, serta memastikan nilai tersebut tetap dikirim saat filter kategori digunakan sehingga input tetap terisi (state persistence pada form search)</t>
+  </si>
+  <si>
+    <t>Pengembangan UI/UX dan struktur halaman sistem (dashboard, form, dan layout fitur). Penyusunan kerangka tampilan halaman admin serta integrasi awal dengan backend PHP.</t>
+  </si>
+  <si>
+    <t>Melakukan pengembangan dan penyempurnaan tampilan antarmuka sistem dengan menggunakan CSS. Fokus pada layout dashboard, card fitur, form input, dan komponen notifikasi agar lebih responsif dan konsisten di seluruh halaman.</t>
+  </si>
+  <si>
+    <t>Validasi Peminjaman &amp; Pengembalian + Notifikasi</t>
+  </si>
+  <si>
+    <t>Notifikasi hanya muncul pada badge (angka), tetapi tidak tampil pada dropdown notifikasi meskipun data sudah ada di database</t>
+  </si>
+  <si>
+    <t>1. Admin melakukan validasi peminjaman/pengembalian buku
+2. Sistem berhasil membuat notifikasi dan badge bertambah
+3. Dropdown notifikasi dibuka tetapi tidak menampilkan data</t>
+  </si>
+  <si>
+    <t>Melakukan pengecekan pada endpoint API notifikasi, menyesuaikan query berdasarkan role user (admin/anggota), serta memastikan data dari database dikirim dalam format JSON yang benar agar dapat dirender oleh frontend</t>
+  </si>
+  <si>
+    <t>Kelola Anggota, Transaksi, &amp; Laporan Buku</t>
+  </si>
+  <si>
+    <t>Pesan “Tidak ada data transaksi pada periode ini” dan “Tidak ada data buku” sudah dibuat, namun tidak muncul saat data kosong sehingga halaman terlihat kosong tanpa informasi</t>
+  </si>
+  <si>
+    <t>1. Masuk ke halaman laporan transaksi / buku
+2. Filter periode tertentu yang tidak memiliki data
+3. Kondisi empty state sudah diimplementasikan tetapi tidak terpanggil di UI</t>
+  </si>
+  <si>
+    <t>Memperbaiki kondisi pengecekan data kosong (empty($lap_transaksi) dan empty($lap_buku)) serta memastikan blok HTML empty state berada pada alur render yang benar</t>
+  </si>
+  <si>
+    <t>Perancangan dan Implementasi Footer Aplikasi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -329,6 +487,19 @@
       <sz val="10"/>
       <color rgb="FFFF0000"/>
       <name val="&quot;Google Sans Text&quot;"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="&quot;Google Sans Text&quot;"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -366,22 +537,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -400,7 +563,73 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -626,287 +855,441 @@
   <dimension ref="A1:G24"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.7109375" customWidth="1"/>
-    <col min="4" max="4" width="21.42578125" customWidth="1"/>
-    <col min="5" max="5" width="23.85546875" customWidth="1"/>
-    <col min="6" max="6" width="34.28515625" customWidth="1"/>
-    <col min="7" max="7" width="19.85546875" customWidth="1"/>
+    <col min="1" max="1" width="6.7109375" style="15" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" style="18"/>
+    <col min="3" max="3" width="50.7109375" style="31" customWidth="1"/>
+    <col min="4" max="6" width="35.7109375" style="15" customWidth="1"/>
+    <col min="7" max="7" width="19.85546875" style="15" customWidth="1"/>
+    <col min="8" max="16384" width="12.5703125" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:7" ht="12.75">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="12" t="s">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" ht="12.75">
+      <c r="A2" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+    </row>
+    <row r="3" spans="1:7" ht="12.75">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" ht="50.1" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" s="21" customFormat="1" ht="80.099999999999994" customHeight="1">
+      <c r="A5" s="19">
         <v>1</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" ht="50.1" customHeight="1">
-      <c r="A4" s="3" t="s">
+      <c r="B5" s="20">
+        <v>46118</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>95</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="G5" s="19" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="79.5" customHeight="1">
+      <c r="A6" s="16">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B6" s="17">
+        <v>46119</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="80.099999999999994" customHeight="1">
+      <c r="A7" s="16">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="B7" s="17">
+        <v>46120</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" s="18" customFormat="1" ht="80.099999999999994" customHeight="1">
+      <c r="A8" s="16">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="B8" s="17">
+        <v>46121</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="80.099999999999994" customHeight="1">
+      <c r="A9" s="16">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="B9" s="17">
+        <v>46122</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
+      <c r="G9" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="80.099999999999994" customHeight="1">
+      <c r="A10" s="16">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="B10" s="23">
+        <v>46123</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="F10" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="80.099999999999994" customHeight="1">
+      <c r="A11" s="16">
         <v>7</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="B11" s="23">
+        <v>46124</v>
+      </c>
+      <c r="C11" s="29" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="80.099999999999994" customHeight="1">
+      <c r="A12" s="16">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="4">
-        <v>1</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="4">
-        <v>2</v>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="4">
-        <v>3</v>
-      </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="4">
-        <v>4</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="4">
-        <v>5</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="4">
-        <v>6</v>
-      </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="5"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="4">
-        <v>7</v>
-      </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="5"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="4">
-        <v>8</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="5"/>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="4">
+      <c r="B12" s="25">
+        <v>46125</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>118</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="80.099999999999994" customHeight="1">
+      <c r="A13" s="16">
         <v>9</v>
       </c>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="5"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="4">
+      <c r="B13" s="23">
+        <v>46126</v>
+      </c>
+      <c r="C13" s="29" t="s">
+        <v>122</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="F13" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="80.099999999999994" customHeight="1">
+      <c r="A14" s="16">
         <v>10</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="5"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="4">
+      <c r="B14" s="23">
+        <v>46127</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="D14" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="F14" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="80.099999999999994" customHeight="1">
+      <c r="A15" s="16">
         <v>11</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="5"/>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="4">
+      <c r="B15" s="23">
+        <v>46128</v>
+      </c>
+      <c r="C15" s="29" t="s">
+        <v>132</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>133</v>
+      </c>
+      <c r="E15" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="F15" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="80.099999999999994" customHeight="1">
+      <c r="A16" s="16">
         <v>12</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="5"/>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="4">
+      <c r="B16" s="23">
+        <v>46129</v>
+      </c>
+      <c r="C16" s="29" t="s">
+        <v>130</v>
+      </c>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="80.099999999999994" customHeight="1">
+      <c r="A17" s="16">
         <v>13</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="5"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="4">
+      <c r="B17" s="23">
+        <v>46130</v>
+      </c>
+      <c r="C17" s="29" t="s">
+        <v>131</v>
+      </c>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="80.099999999999994" customHeight="1">
+      <c r="A18" s="16">
         <v>14</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="5"/>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="4">
+      <c r="B18" s="23">
+        <v>46131</v>
+      </c>
+      <c r="C18" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="E18" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="F18" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="80.099999999999994" customHeight="1">
+      <c r="A19" s="16">
         <v>15</v>
       </c>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="5"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="4">
+      <c r="B19" s="23">
+        <v>46132</v>
+      </c>
+      <c r="C19" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="14"/>
+    </row>
+    <row r="20" spans="1:7" ht="12.75">
+      <c r="A20" s="16">
         <v>16</v>
       </c>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6"/>
-      <c r="E20" s="6"/>
-      <c r="F20" s="6"/>
-      <c r="G20" s="5"/>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="4">
+      <c r="B20" s="28"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="14"/>
+    </row>
+    <row r="21" spans="1:7" ht="12.75">
+      <c r="A21" s="16">
         <v>17</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="5"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="4">
+      <c r="B21" s="28"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="14"/>
+    </row>
+    <row r="22" spans="1:7" ht="12.75">
+      <c r="A22" s="16">
         <v>18</v>
       </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="5"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="4">
+      <c r="B22" s="28"/>
+      <c r="C22" s="30"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="14"/>
+    </row>
+    <row r="23" spans="1:7" ht="12.75">
+      <c r="A23" s="16">
         <v>19</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="5"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="4">
+      <c r="B23" s="28"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="14"/>
+    </row>
+    <row r="24" spans="1:7" ht="12.75">
+      <c r="A24" s="16">
         <v>20</v>
       </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="5"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -919,6 +1302,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -941,1213 +1325,1213 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:27">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:27">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:27">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="J4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8"/>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="8"/>
-      <c r="V4" s="8"/>
-      <c r="W4" s="8"/>
-      <c r="X4" s="8"/>
-      <c r="Y4" s="8"/>
-      <c r="Z4" s="8"/>
-      <c r="AA4" s="8"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="4"/>
+      <c r="S4" s="4"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="4"/>
+      <c r="V4" s="4"/>
+      <c r="W4" s="4"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4"/>
+      <c r="Z4" s="4"/>
+      <c r="AA4" s="4"/>
     </row>
     <row r="5" spans="1:27">
-      <c r="A5" s="9">
+      <c r="A5" s="5">
         <v>1</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9" t="s">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="H5" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="J5" s="11"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="8"/>
-      <c r="V5" s="8"/>
-      <c r="W5" s="8"/>
-      <c r="X5" s="8"/>
-      <c r="Y5" s="8"/>
-      <c r="Z5" s="8"/>
-      <c r="AA5" s="8"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4"/>
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4"/>
+      <c r="Z5" s="4"/>
+      <c r="AA5" s="4"/>
     </row>
     <row r="6" spans="1:27">
-      <c r="A6" s="9">
+      <c r="A6" s="5">
         <v>2</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="11"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="8"/>
-      <c r="U6" s="8"/>
-      <c r="V6" s="8"/>
-      <c r="W6" s="8"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="8"/>
-      <c r="Z6" s="8"/>
-      <c r="AA6" s="8"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4"/>
+      <c r="V6" s="4"/>
+      <c r="W6" s="4"/>
+      <c r="X6" s="4"/>
+      <c r="Y6" s="4"/>
+      <c r="Z6" s="4"/>
+      <c r="AA6" s="4"/>
     </row>
     <row r="7" spans="1:27">
-      <c r="A7" s="9">
+      <c r="A7" s="5">
         <v>3</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="5"/>
+      <c r="C7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="11"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="8"/>
-      <c r="V7" s="8"/>
-      <c r="W7" s="8"/>
-      <c r="X7" s="8"/>
-      <c r="Y7" s="8"/>
-      <c r="Z7" s="8"/>
-      <c r="AA7" s="8"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4"/>
+      <c r="V7" s="4"/>
+      <c r="W7" s="4"/>
+      <c r="X7" s="4"/>
+      <c r="Y7" s="4"/>
+      <c r="Z7" s="4"/>
+      <c r="AA7" s="4"/>
     </row>
     <row r="8" spans="1:27">
-      <c r="A8" s="9">
+      <c r="A8" s="5">
         <v>4</v>
       </c>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9" t="s">
+      <c r="B8" s="5"/>
+      <c r="C8" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="11"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="8"/>
-      <c r="V8" s="8"/>
-      <c r="W8" s="8"/>
-      <c r="X8" s="8"/>
-      <c r="Y8" s="8"/>
-      <c r="Z8" s="8"/>
-      <c r="AA8" s="8"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4"/>
+      <c r="V8" s="4"/>
+      <c r="W8" s="4"/>
+      <c r="X8" s="4"/>
+      <c r="Y8" s="4"/>
+      <c r="Z8" s="4"/>
+      <c r="AA8" s="4"/>
     </row>
     <row r="9" spans="1:27">
-      <c r="A9" s="9">
+      <c r="A9" s="5">
         <v>5</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9" t="s">
+      <c r="B9" s="5"/>
+      <c r="C9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="11"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
-      <c r="U9" s="8"/>
-      <c r="V9" s="8"/>
-      <c r="W9" s="8"/>
-      <c r="X9" s="8"/>
-      <c r="Y9" s="8"/>
-      <c r="Z9" s="8"/>
-      <c r="AA9" s="8"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="V9" s="4"/>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="4"/>
+      <c r="AA9" s="4"/>
     </row>
     <row r="10" spans="1:27">
-      <c r="A10" s="9">
+      <c r="A10" s="5">
         <v>6</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9" t="s">
+      <c r="B10" s="5"/>
+      <c r="C10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="11"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-      <c r="S10" s="8"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="8"/>
-      <c r="V10" s="8"/>
-      <c r="W10" s="8"/>
-      <c r="X10" s="8"/>
-      <c r="Y10" s="8"/>
-      <c r="Z10" s="8"/>
-      <c r="AA10" s="8"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4"/>
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+      <c r="X10" s="4"/>
+      <c r="Y10" s="4"/>
+      <c r="Z10" s="4"/>
+      <c r="AA10" s="4"/>
     </row>
     <row r="11" spans="1:27">
-      <c r="A11" s="9">
+      <c r="A11" s="5">
         <v>7</v>
       </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9" t="s">
+      <c r="B11" s="5"/>
+      <c r="C11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="11"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="8"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="8"/>
-      <c r="W11" s="8"/>
-      <c r="X11" s="8"/>
-      <c r="Y11" s="8"/>
-      <c r="Z11" s="8"/>
-      <c r="AA11" s="8"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4"/>
+      <c r="V11" s="4"/>
+      <c r="W11" s="4"/>
+      <c r="X11" s="4"/>
+      <c r="Y11" s="4"/>
+      <c r="Z11" s="4"/>
+      <c r="AA11" s="4"/>
     </row>
     <row r="12" spans="1:27">
-      <c r="A12" s="9">
+      <c r="A12" s="5">
         <v>8</v>
       </c>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9" t="s">
+      <c r="B12" s="5"/>
+      <c r="C12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="8"/>
-      <c r="V12" s="8"/>
-      <c r="W12" s="8"/>
-      <c r="X12" s="8"/>
-      <c r="Y12" s="8"/>
-      <c r="Z12" s="8"/>
-      <c r="AA12" s="8"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4"/>
+      <c r="V12" s="4"/>
+      <c r="W12" s="4"/>
+      <c r="X12" s="4"/>
+      <c r="Y12" s="4"/>
+      <c r="Z12" s="4"/>
+      <c r="AA12" s="4"/>
     </row>
     <row r="13" spans="1:27">
-      <c r="A13" s="9">
+      <c r="A13" s="5">
         <v>9</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9" t="s">
+      <c r="B13" s="5"/>
+      <c r="C13" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="9" t="s">
+      <c r="D13" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E13" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="H13" s="9" t="s">
+      <c r="H13" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="8"/>
-      <c r="U13" s="8"/>
-      <c r="V13" s="8"/>
-      <c r="W13" s="8"/>
-      <c r="X13" s="8"/>
-      <c r="Y13" s="8"/>
-      <c r="Z13" s="8"/>
-      <c r="AA13" s="8"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4"/>
+      <c r="V13" s="4"/>
+      <c r="W13" s="4"/>
+      <c r="X13" s="4"/>
+      <c r="Y13" s="4"/>
+      <c r="Z13" s="4"/>
+      <c r="AA13" s="4"/>
     </row>
     <row r="14" spans="1:27">
-      <c r="A14" s="9">
+      <c r="A14" s="5">
         <v>10</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9" t="s">
+      <c r="B14" s="5"/>
+      <c r="C14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="9" t="s">
+      <c r="D14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="9" t="s">
+      <c r="E14" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="I14" s="11"/>
-      <c r="J14" s="11"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
-      <c r="S14" s="8"/>
-      <c r="T14" s="8"/>
-      <c r="U14" s="8"/>
-      <c r="V14" s="8"/>
-      <c r="W14" s="8"/>
-      <c r="X14" s="8"/>
-      <c r="Y14" s="8"/>
-      <c r="Z14" s="8"/>
-      <c r="AA14" s="8"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
+      <c r="X14" s="4"/>
+      <c r="Y14" s="4"/>
+      <c r="Z14" s="4"/>
+      <c r="AA14" s="4"/>
     </row>
     <row r="15" spans="1:27">
-      <c r="A15" s="9">
+      <c r="A15" s="5">
         <v>11</v>
       </c>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9" t="s">
+      <c r="B15" s="5"/>
+      <c r="C15" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E15" s="9" t="s">
+      <c r="E15" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="8"/>
-      <c r="T15" s="8"/>
-      <c r="U15" s="8"/>
-      <c r="V15" s="8"/>
-      <c r="W15" s="8"/>
-      <c r="X15" s="8"/>
-      <c r="Y15" s="8"/>
-      <c r="Z15" s="8"/>
-      <c r="AA15" s="8"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
+      <c r="U15" s="4"/>
+      <c r="V15" s="4"/>
+      <c r="W15" s="4"/>
+      <c r="X15" s="4"/>
+      <c r="Y15" s="4"/>
+      <c r="Z15" s="4"/>
+      <c r="AA15" s="4"/>
     </row>
     <row r="16" spans="1:27">
-      <c r="A16" s="9">
+      <c r="A16" s="5">
         <v>12</v>
       </c>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9" t="s">
+      <c r="B16" s="5"/>
+      <c r="C16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="9" t="s">
+      <c r="D16" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="9" t="s">
+      <c r="E16" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="8"/>
-      <c r="T16" s="8"/>
-      <c r="U16" s="8"/>
-      <c r="V16" s="8"/>
-      <c r="W16" s="8"/>
-      <c r="X16" s="8"/>
-      <c r="Y16" s="8"/>
-      <c r="Z16" s="8"/>
-      <c r="AA16" s="8"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="4"/>
+      <c r="W16" s="4"/>
+      <c r="X16" s="4"/>
+      <c r="Y16" s="4"/>
+      <c r="Z16" s="4"/>
+      <c r="AA16" s="4"/>
     </row>
     <row r="17" spans="1:27">
-      <c r="A17" s="9">
+      <c r="A17" s="5">
         <v>13</v>
       </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9" t="s">
+      <c r="B17" s="5"/>
+      <c r="C17" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="9" t="s">
+      <c r="D17" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="9" t="s">
+      <c r="E17" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="H17" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="8"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="8"/>
-      <c r="V17" s="8"/>
-      <c r="W17" s="8"/>
-      <c r="X17" s="8"/>
-      <c r="Y17" s="8"/>
-      <c r="Z17" s="8"/>
-      <c r="AA17" s="8"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="4"/>
+      <c r="Z17" s="4"/>
+      <c r="AA17" s="4"/>
     </row>
     <row r="18" spans="1:27">
-      <c r="A18" s="9">
+      <c r="A18" s="5">
         <v>14</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9" t="s">
+      <c r="B18" s="5"/>
+      <c r="C18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="9" t="s">
+      <c r="D18" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="9" t="s">
+      <c r="E18" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="H18" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="8"/>
-      <c r="W18" s="8"/>
-      <c r="X18" s="8"/>
-      <c r="Y18" s="8"/>
-      <c r="Z18" s="8"/>
-      <c r="AA18" s="8"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="4"/>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="4"/>
+      <c r="W18" s="4"/>
+      <c r="X18" s="4"/>
+      <c r="Y18" s="4"/>
+      <c r="Z18" s="4"/>
+      <c r="AA18" s="4"/>
     </row>
     <row r="19" spans="1:27">
-      <c r="A19" s="9">
+      <c r="A19" s="5">
         <v>15</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9" t="s">
+      <c r="B19" s="5"/>
+      <c r="C19" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D19" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="H19" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="8"/>
-      <c r="S19" s="8"/>
-      <c r="T19" s="8"/>
-      <c r="U19" s="8"/>
-      <c r="V19" s="8"/>
-      <c r="W19" s="8"/>
-      <c r="X19" s="8"/>
-      <c r="Y19" s="8"/>
-      <c r="Z19" s="8"/>
-      <c r="AA19" s="8"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="4"/>
+      <c r="W19" s="4"/>
+      <c r="X19" s="4"/>
+      <c r="Y19" s="4"/>
+      <c r="Z19" s="4"/>
+      <c r="AA19" s="4"/>
     </row>
     <row r="20" spans="1:27">
-      <c r="A20" s="9">
+      <c r="A20" s="5">
         <v>16</v>
       </c>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9" t="s">
+      <c r="B20" s="5"/>
+      <c r="C20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E20" s="9" t="s">
+      <c r="E20" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="8"/>
-      <c r="L20" s="8"/>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="8"/>
-      <c r="Q20" s="8"/>
-      <c r="R20" s="8"/>
-      <c r="S20" s="8"/>
-      <c r="T20" s="8"/>
-      <c r="U20" s="8"/>
-      <c r="V20" s="8"/>
-      <c r="W20" s="8"/>
-      <c r="X20" s="8"/>
-      <c r="Y20" s="8"/>
-      <c r="Z20" s="8"/>
-      <c r="AA20" s="8"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="4"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="4"/>
+      <c r="T20" s="4"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="4"/>
+      <c r="W20" s="4"/>
+      <c r="X20" s="4"/>
+      <c r="Y20" s="4"/>
+      <c r="Z20" s="4"/>
+      <c r="AA20" s="4"/>
     </row>
     <row r="21" spans="1:27">
-      <c r="A21" s="9">
+      <c r="A21" s="5">
         <v>17</v>
       </c>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9" t="s">
+      <c r="B21" s="5"/>
+      <c r="C21" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="9" t="s">
+      <c r="D21" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="H21" s="9" t="s">
+      <c r="H21" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="I21" s="11"/>
-      <c r="J21" s="11"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="8"/>
-      <c r="Q21" s="8"/>
-      <c r="R21" s="8"/>
-      <c r="S21" s="8"/>
-      <c r="T21" s="8"/>
-      <c r="U21" s="8"/>
-      <c r="V21" s="8"/>
-      <c r="W21" s="8"/>
-      <c r="X21" s="8"/>
-      <c r="Y21" s="8"/>
-      <c r="Z21" s="8"/>
-      <c r="AA21" s="8"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="4"/>
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="4"/>
+      <c r="T21" s="4"/>
+      <c r="U21" s="4"/>
+      <c r="V21" s="4"/>
+      <c r="W21" s="4"/>
+      <c r="X21" s="4"/>
+      <c r="Y21" s="4"/>
+      <c r="Z21" s="4"/>
+      <c r="AA21" s="4"/>
     </row>
     <row r="22" spans="1:27">
-      <c r="A22" s="9">
+      <c r="A22" s="5">
         <v>18</v>
       </c>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9" t="s">
+      <c r="B22" s="5"/>
+      <c r="C22" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="9" t="s">
+      <c r="D22" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E22" s="9" t="s">
+      <c r="E22" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="H22" s="9" t="s">
+      <c r="H22" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11"/>
-      <c r="K22" s="8"/>
-      <c r="L22" s="8"/>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
-      <c r="P22" s="8"/>
-      <c r="Q22" s="8"/>
-      <c r="R22" s="8"/>
-      <c r="S22" s="8"/>
-      <c r="T22" s="8"/>
-      <c r="U22" s="8"/>
-      <c r="V22" s="8"/>
-      <c r="W22" s="8"/>
-      <c r="X22" s="8"/>
-      <c r="Y22" s="8"/>
-      <c r="Z22" s="8"/>
-      <c r="AA22" s="8"/>
+      <c r="I22" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4"/>
+      <c r="O22" s="4"/>
+      <c r="P22" s="4"/>
+      <c r="Q22" s="4"/>
+      <c r="R22" s="4"/>
+      <c r="S22" s="4"/>
+      <c r="T22" s="4"/>
+      <c r="U22" s="4"/>
+      <c r="V22" s="4"/>
+      <c r="W22" s="4"/>
+      <c r="X22" s="4"/>
+      <c r="Y22" s="4"/>
+      <c r="Z22" s="4"/>
+      <c r="AA22" s="4"/>
     </row>
     <row r="23" spans="1:27">
-      <c r="A23" s="9">
+      <c r="A23" s="5">
         <v>19</v>
       </c>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9" t="s">
+      <c r="B23" s="5"/>
+      <c r="C23" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D23" s="9" t="s">
+      <c r="D23" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="H23" s="9" t="s">
+      <c r="H23" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="I23" s="11"/>
-      <c r="J23" s="11"/>
-      <c r="K23" s="8"/>
-      <c r="L23" s="8"/>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="8"/>
-      <c r="P23" s="8"/>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="8"/>
-      <c r="S23" s="8"/>
-      <c r="T23" s="8"/>
-      <c r="U23" s="8"/>
-      <c r="V23" s="8"/>
-      <c r="W23" s="8"/>
-      <c r="X23" s="8"/>
-      <c r="Y23" s="8"/>
-      <c r="Z23" s="8"/>
-      <c r="AA23" s="8"/>
+      <c r="I23" s="7"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="4"/>
+      <c r="T23" s="4"/>
+      <c r="U23" s="4"/>
+      <c r="V23" s="4"/>
+      <c r="W23" s="4"/>
+      <c r="X23" s="4"/>
+      <c r="Y23" s="4"/>
+      <c r="Z23" s="4"/>
+      <c r="AA23" s="4"/>
     </row>
     <row r="24" spans="1:27">
-      <c r="A24" s="9">
+      <c r="A24" s="5">
         <v>20</v>
       </c>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9" t="s">
+      <c r="B24" s="5"/>
+      <c r="C24" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="D24" s="9" t="s">
+      <c r="D24" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="H24" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
-      <c r="S24" s="8"/>
-      <c r="T24" s="8"/>
-      <c r="U24" s="8"/>
-      <c r="V24" s="8"/>
-      <c r="W24" s="8"/>
-      <c r="X24" s="8"/>
-      <c r="Y24" s="8"/>
-      <c r="Z24" s="8"/>
-      <c r="AA24" s="8"/>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4"/>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="4"/>
+      <c r="X24" s="4"/>
+      <c r="Y24" s="4"/>
+      <c r="Z24" s="4"/>
+      <c r="AA24" s="4"/>
     </row>
     <row r="25" spans="1:27">
-      <c r="A25" s="9">
+      <c r="A25" s="5">
         <v>21</v>
       </c>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9" t="s">
+      <c r="B25" s="5"/>
+      <c r="C25" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F25" s="9" t="s">
+      <c r="F25" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G25" s="9" t="s">
+      <c r="G25" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H25" s="9" t="s">
+      <c r="H25" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8"/>
-      <c r="Q25" s="8"/>
-      <c r="R25" s="8"/>
-      <c r="S25" s="8"/>
-      <c r="T25" s="8"/>
-      <c r="U25" s="8"/>
-      <c r="V25" s="8"/>
-      <c r="W25" s="8"/>
-      <c r="X25" s="8"/>
-      <c r="Y25" s="8"/>
-      <c r="Z25" s="8"/>
-      <c r="AA25" s="8"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4"/>
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="4"/>
+      <c r="T25" s="4"/>
+      <c r="U25" s="4"/>
+      <c r="V25" s="4"/>
+      <c r="W25" s="4"/>
+      <c r="X25" s="4"/>
+      <c r="Y25" s="4"/>
+      <c r="Z25" s="4"/>
+      <c r="AA25" s="4"/>
     </row>
     <row r="26" spans="1:27">
-      <c r="A26" s="9">
+      <c r="A26" s="5">
         <v>22</v>
       </c>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9" t="s">
+      <c r="B26" s="5"/>
+      <c r="C26" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D26" s="9" t="s">
+      <c r="D26" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E26" s="9" t="s">
+      <c r="E26" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F26" s="9" t="s">
+      <c r="F26" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G26" s="9" t="s">
+      <c r="G26" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="H26" s="9" t="s">
+      <c r="H26" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="8"/>
-      <c r="Q26" s="8"/>
-      <c r="R26" s="8"/>
-      <c r="S26" s="8"/>
-      <c r="T26" s="8"/>
-      <c r="U26" s="8"/>
-      <c r="V26" s="8"/>
-      <c r="W26" s="8"/>
-      <c r="X26" s="8"/>
-      <c r="Y26" s="8"/>
-      <c r="Z26" s="8"/>
-      <c r="AA26" s="8"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
+      <c r="P26" s="4"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+      <c r="S26" s="4"/>
+      <c r="T26" s="4"/>
+      <c r="U26" s="4"/>
+      <c r="V26" s="4"/>
+      <c r="W26" s="4"/>
+      <c r="X26" s="4"/>
+      <c r="Y26" s="4"/>
+      <c r="Z26" s="4"/>
+      <c r="AA26" s="4"/>
     </row>
     <row r="27" spans="1:27">
-      <c r="A27" s="9">
+      <c r="A27" s="5">
         <v>23</v>
       </c>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9" t="s">
+      <c r="B27" s="5"/>
+      <c r="C27" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F27" s="9" t="s">
+      <c r="F27" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="H27" s="9" t="s">
+      <c r="H27" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="8"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="8"/>
-      <c r="P27" s="8"/>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="8"/>
-      <c r="S27" s="8"/>
-      <c r="T27" s="8"/>
-      <c r="U27" s="8"/>
-      <c r="V27" s="8"/>
-      <c r="W27" s="8"/>
-      <c r="X27" s="8"/>
-      <c r="Y27" s="8"/>
-      <c r="Z27" s="8"/>
-      <c r="AA27" s="8"/>
+      <c r="I27" s="7"/>
+      <c r="J27" s="7"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="4"/>
+      <c r="T27" s="4"/>
+      <c r="U27" s="4"/>
+      <c r="V27" s="4"/>
+      <c r="W27" s="4"/>
+      <c r="X27" s="4"/>
+      <c r="Y27" s="4"/>
+      <c r="Z27" s="4"/>
+      <c r="AA27" s="4"/>
     </row>
     <row r="28" spans="1:27">
-      <c r="A28" s="9">
+      <c r="A28" s="5">
         <v>24</v>
       </c>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9" t="s">
+      <c r="B28" s="5"/>
+      <c r="C28" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="D28" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E28" s="9" t="s">
+      <c r="E28" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G28" s="9" t="s">
+      <c r="G28" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="H28" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="8"/>
-      <c r="P28" s="8"/>
-      <c r="Q28" s="8"/>
-      <c r="R28" s="8"/>
-      <c r="S28" s="8"/>
-      <c r="T28" s="8"/>
-      <c r="U28" s="8"/>
-      <c r="V28" s="8"/>
-      <c r="W28" s="8"/>
-      <c r="X28" s="8"/>
-      <c r="Y28" s="8"/>
-      <c r="Z28" s="8"/>
-      <c r="AA28" s="8"/>
+      <c r="I28" s="7"/>
+      <c r="J28" s="7"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="4"/>
+      <c r="Q28" s="4"/>
+      <c r="R28" s="4"/>
+      <c r="S28" s="4"/>
+      <c r="T28" s="4"/>
+      <c r="U28" s="4"/>
+      <c r="V28" s="4"/>
+      <c r="W28" s="4"/>
+      <c r="X28" s="4"/>
+      <c r="Y28" s="4"/>
+      <c r="Z28" s="4"/>
+      <c r="AA28" s="4"/>
     </row>
     <row r="29" spans="1:27">
-      <c r="A29" s="9">
+      <c r="A29" s="5">
         <v>25</v>
       </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9" t="s">
+      <c r="B29" s="5"/>
+      <c r="C29" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="D29" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E29" s="9" t="s">
+      <c r="E29" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F29" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G29" s="9" t="s">
+      <c r="G29" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="H29" s="9" t="s">
+      <c r="H29" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8"/>
-      <c r="Q29" s="8"/>
-      <c r="R29" s="8"/>
-      <c r="S29" s="8"/>
-      <c r="T29" s="8"/>
-      <c r="U29" s="8"/>
-      <c r="V29" s="8"/>
-      <c r="W29" s="8"/>
-      <c r="X29" s="8"/>
-      <c r="Y29" s="8"/>
-      <c r="Z29" s="8"/>
-      <c r="AA29" s="8"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="7"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="4"/>
+      <c r="R29" s="4"/>
+      <c r="S29" s="4"/>
+      <c r="T29" s="4"/>
+      <c r="U29" s="4"/>
+      <c r="V29" s="4"/>
+      <c r="W29" s="4"/>
+      <c r="X29" s="4"/>
+      <c r="Y29" s="4"/>
+      <c r="Z29" s="4"/>
+      <c r="AA29" s="4"/>
     </row>
     <row r="30" spans="1:27">
-      <c r="A30" s="9">
+      <c r="A30" s="5">
         <v>26</v>
       </c>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9" t="s">
+      <c r="B30" s="5"/>
+      <c r="C30" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D30" s="9" t="s">
+      <c r="D30" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E30" s="9" t="s">
+      <c r="E30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="F30" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G30" s="9" t="s">
+      <c r="G30" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="H30" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
-      <c r="P30" s="8"/>
-      <c r="Q30" s="8"/>
-      <c r="R30" s="8"/>
-      <c r="S30" s="8"/>
-      <c r="T30" s="8"/>
-      <c r="U30" s="8"/>
-      <c r="V30" s="8"/>
-      <c r="W30" s="8"/>
-      <c r="X30" s="8"/>
-      <c r="Y30" s="8"/>
-      <c r="Z30" s="8"/>
-      <c r="AA30" s="8"/>
+      <c r="I30" s="7"/>
+      <c r="J30" s="7"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
+      <c r="P30" s="4"/>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="4"/>
+      <c r="S30" s="4"/>
+      <c r="T30" s="4"/>
+      <c r="U30" s="4"/>
+      <c r="V30" s="4"/>
+      <c r="W30" s="4"/>
+      <c r="X30" s="4"/>
+      <c r="Y30" s="4"/>
+      <c r="Z30" s="4"/>
+      <c r="AA30" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Format Debugging dan Pengujian.xlsx
+++ b/Format Debugging dan Pengujian.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\peminjaman_buku\debug_&amp;_pengujian_webPeminjamanBuku\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98DE32F7-0F00-4BCF-BAF9-BF2B080EE91F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F05306-2066-4AF2-8DD6-2B6C9BB31DD8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="229">
   <si>
     <t xml:space="preserve">NIS : </t>
   </si>
@@ -700,6 +700,120 @@
   </si>
   <si>
     <t>Sistem tetap mengarahkan ke halaman login tanpa membuat akun</t>
+  </si>
+  <si>
+    <t>Pencarian Buku</t>
+  </si>
+  <si>
+    <t>Read</t>
+  </si>
+  <si>
+    <t>User mencari buku melalui kolom pencarian</t>
+  </si>
+  <si>
+    <t>Sistem menampilkan daftar buku sesuai keyword</t>
+  </si>
+  <si>
+    <t>User memilih kategori setelah melakukan pencarian</t>
+  </si>
+  <si>
+    <t>Sistem memfilter dan menampilkan buku sesuai kategori yang dipilih</t>
+  </si>
+  <si>
+    <t>User menekan tombol reset setelah filter kategori</t>
+  </si>
+  <si>
+    <t>Sistem mengembalikan tampilan ke halaman awal (semua buku)</t>
+  </si>
+  <si>
+    <t>Peminjaman Buku</t>
+  </si>
+  <si>
+    <t>Create</t>
+  </si>
+  <si>
+    <t>User melakukan peminjaman dengan jumlah buku sesuai stok dan mengisi tanggal peminjaman</t>
+  </si>
+  <si>
+    <t>Sistem berhasil memproses peminjaman</t>
+  </si>
+  <si>
+    <t>Setelah peminjaman berhasil, sistem menampilkan daftar buku yang dipinjam</t>
+  </si>
+  <si>
+    <t>Buku muncul di halaman daftar peminjaman dengan status "menunggu validasi"</t>
+  </si>
+  <si>
+    <t>Setelah user melakukan peminjaman</t>
+  </si>
+  <si>
+    <t>Sistem mengirim notifikasi ke anggota dan admin</t>
+  </si>
+  <si>
+    <t>Admin melakukan validasi peminjaman buku</t>
+  </si>
+  <si>
+    <t>Status peminjaman berubah menjadi disetujui</t>
+  </si>
+  <si>
+    <t>Setelah admin menyetujui peminjaman</t>
+  </si>
+  <si>
+    <t>Sistem mengirim notifikasi ke anggota bahwa peminjaman telah disetujui</t>
+  </si>
+  <si>
+    <t>User melihat status peminjaman setelah divalidasi admin</t>
+  </si>
+  <si>
+    <t>Status berubah dari "menunggu validasi" menjadi "disetujui"</t>
+  </si>
+  <si>
+    <t>Validasi Admin</t>
+  </si>
+  <si>
+    <t>Notifikasi</t>
+  </si>
+  <si>
+    <t>User mencari buku dengan keyword yang tidak ada</t>
+  </si>
+  <si>
+    <t>Sistem menampilkan pesan “data tidak ditemukan”</t>
+  </si>
+  <si>
+    <t>User memilih kategori yang tidak memiliki buku</t>
+  </si>
+  <si>
+    <t>Sistem menampilkan daftar kosong atau pesan tidak ada data</t>
+  </si>
+  <si>
+    <t>User menekan tombol "Pinjam" pada buku yang stoknya habis</t>
+  </si>
+  <si>
+    <t>Sistem menolak dan menampilkan pesan “stok tidak tersedia”</t>
+  </si>
+  <si>
+    <t>User menginput jumlah peminjaman = 0</t>
+  </si>
+  <si>
+    <t>Sistem menolak dan menampilkan validasi jumlah minimal</t>
+  </si>
+  <si>
+    <t>User menginput jumlah peminjaman melebihi stok tersedia</t>
+  </si>
+  <si>
+    <t>Sistem menolak dan menampilkan pesan “stok tidak mencukupi”</t>
+  </si>
+  <si>
+    <t>User tidak mengisi tanggal peminjaman</t>
+  </si>
+  <si>
+    <t>Sistem menolak dan menampilkan validasi field wajib</t>
+  </si>
+  <si>
+    <t>User mencoba meminjam buku saat akun di nonaktifkan admin</t>
+  </si>
+  <si>
+    <t>Sistem menolak akses dan memberikan notifikasi akun dinonaktifkan</t>
   </si>
 </sst>
 </file>
@@ -813,7 +927,7 @@
       <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -874,8 +988,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -913,11 +1033,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -958,147 +1091,164 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="10" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1322,369 +1472,369 @@
   <dimension ref="A1:I18"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" style="23" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" style="23"/>
-    <col min="3" max="3" width="50.7109375" style="29" customWidth="1"/>
-    <col min="4" max="6" width="35.7109375" style="23" customWidth="1"/>
-    <col min="7" max="7" width="19.85546875" style="23" customWidth="1"/>
-    <col min="8" max="8" width="25.5703125" style="38" customWidth="1"/>
-    <col min="9" max="9" width="36.85546875" style="23" customWidth="1"/>
-    <col min="10" max="16384" width="12.5703125" style="23"/>
+    <col min="1" max="1" width="6.7109375" style="19" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" style="19"/>
+    <col min="3" max="3" width="50.7109375" style="25" customWidth="1"/>
+    <col min="4" max="6" width="35.7109375" style="19" customWidth="1"/>
+    <col min="7" max="7" width="19.85546875" style="19" customWidth="1"/>
+    <col min="8" max="8" width="25.5703125" style="34" customWidth="1"/>
+    <col min="9" max="9" width="36.85546875" style="19" customWidth="1"/>
+    <col min="10" max="16384" width="12.5703125" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="12.75">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="22"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:9" ht="12.75">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="22"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="18"/>
     </row>
     <row r="3" spans="1:9" ht="12.75">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="22"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="18"/>
     </row>
     <row r="4" spans="1:9" ht="50.1" customHeight="1">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="47" t="s">
+      <c r="H4" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="48" t="s">
+      <c r="I4" s="44" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="79.5" customHeight="1">
-      <c r="A5" s="25"/>
-      <c r="B5" s="26"/>
-      <c r="C5" s="27" t="s">
+      <c r="A5" s="21"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="27" t="s">
+      <c r="F5" s="23" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="G5" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="H5" s="24" t="s">
         <v>151</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="25" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="22" customFormat="1" ht="79.5" customHeight="1">
-      <c r="A6" s="30"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="32" t="s">
+    <row r="6" spans="1:9" s="18" customFormat="1" ht="79.5" customHeight="1">
+      <c r="A6" s="26"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="F6" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="G6" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="33" t="s">
+      <c r="H6" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="34" t="s">
+      <c r="I6" s="30" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="22" customFormat="1" ht="120" customHeight="1">
-      <c r="A7" s="30"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="32" t="s">
+    <row r="7" spans="1:9" s="18" customFormat="1" ht="120" customHeight="1">
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="F7" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="30" t="s">
+      <c r="G7" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="33" t="s">
+      <c r="H7" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="I7" s="46" t="s">
+      <c r="I7" s="42" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="99.95" customHeight="1">
-      <c r="A8" s="25"/>
-      <c r="B8" s="26"/>
-      <c r="C8" s="32" t="s">
+      <c r="A8" s="21"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="F8" s="27" t="s">
+      <c r="F8" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="28" t="s">
+      <c r="H8" s="24" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="80.099999999999994" customHeight="1">
-      <c r="A9" s="25"/>
-      <c r="B9" s="36"/>
-      <c r="C9" s="37" t="s">
+      <c r="A9" s="21"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="37" t="s">
+      <c r="D9" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="37" t="s">
+      <c r="E9" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="37" t="s">
+      <c r="F9" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="21" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="110.1" customHeight="1">
-      <c r="A10" s="25"/>
-      <c r="B10" s="36"/>
-      <c r="C10" s="39" t="s">
+      <c r="A10" s="21"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="35" t="s">
         <v>133</v>
       </c>
-      <c r="D10" s="37" t="s">
+      <c r="D10" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E10" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="37" t="s">
+      <c r="F10" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="21" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="80.099999999999994" customHeight="1">
-      <c r="A11" s="25"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="37" t="s">
+      <c r="A11" s="21"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="D11" s="37" t="s">
+      <c r="D11" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="37" t="s">
+      <c r="E11" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="F11" s="37" t="s">
+      <c r="F11" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="21" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="22" customFormat="1" ht="129.94999999999999" customHeight="1">
-      <c r="A12" s="30"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="39" t="s">
+    <row r="12" spans="1:9" s="18" customFormat="1" ht="129.94999999999999" customHeight="1">
+      <c r="A12" s="26"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="39" t="s">
+      <c r="D12" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="E12" s="39" t="s">
+      <c r="E12" s="35" t="s">
         <v>139</v>
       </c>
-      <c r="F12" s="39" t="s">
+      <c r="F12" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="G12" s="30" t="s">
+      <c r="G12" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="H12" s="35"/>
+      <c r="H12" s="31"/>
     </row>
     <row r="13" spans="1:9" ht="99.95" customHeight="1">
-      <c r="A13" s="25"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="37" t="s">
+      <c r="A13" s="21"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="D13" s="37" t="s">
+      <c r="D13" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="E13" s="37" t="s">
+      <c r="E13" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="F13" s="37" t="s">
+      <c r="F13" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="21" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:9" ht="99.95" customHeight="1">
-      <c r="A14" s="25"/>
-      <c r="B14" s="36"/>
-      <c r="C14" s="37" t="s">
+      <c r="A14" s="21"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="33" t="s">
         <v>141</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="37" t="s">
+      <c r="E14" s="33" t="s">
         <v>140</v>
       </c>
-      <c r="F14" s="37" t="s">
+      <c r="F14" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="21" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="99.95" customHeight="1">
-      <c r="A15" s="25"/>
-      <c r="B15" s="36"/>
-      <c r="C15" s="37" t="s">
+      <c r="A15" s="21"/>
+      <c r="B15" s="32"/>
+      <c r="C15" s="33" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="37" t="s">
+      <c r="D15" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="37" t="s">
+      <c r="E15" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="F15" s="37" t="s">
+      <c r="F15" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="21" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="44" customFormat="1" ht="120" customHeight="1">
-      <c r="A16" s="41"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="43" t="s">
+    <row r="16" spans="1:9" s="40" customFormat="1" ht="120" customHeight="1">
+      <c r="A16" s="37"/>
+      <c r="B16" s="38"/>
+      <c r="C16" s="39" t="s">
         <v>143</v>
       </c>
-      <c r="D16" s="43" t="s">
+      <c r="D16" s="39" t="s">
         <v>144</v>
       </c>
-      <c r="E16" s="43" t="s">
+      <c r="E16" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="F16" s="43" t="s">
+      <c r="F16" s="39" t="s">
         <v>146</v>
       </c>
-      <c r="G16" s="41" t="s">
+      <c r="G16" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="H16" s="45"/>
-    </row>
-    <row r="17" spans="1:8" s="44" customFormat="1" ht="99.95" customHeight="1">
-      <c r="A17" s="41"/>
-      <c r="B17" s="42"/>
-      <c r="C17" s="43" t="s">
+      <c r="H16" s="41"/>
+    </row>
+    <row r="17" spans="1:8" s="40" customFormat="1" ht="99.95" customHeight="1">
+      <c r="A17" s="37"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="39" t="s">
         <v>147</v>
       </c>
-      <c r="D17" s="43" t="s">
+      <c r="D17" s="39" t="s">
         <v>148</v>
       </c>
-      <c r="E17" s="43" t="s">
+      <c r="E17" s="39" t="s">
         <v>149</v>
       </c>
-      <c r="F17" s="43" t="s">
+      <c r="F17" s="39" t="s">
         <v>150</v>
       </c>
-      <c r="G17" s="41" t="s">
+      <c r="G17" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="H17" s="45"/>
-    </row>
-    <row r="18" spans="1:8" s="44" customFormat="1" ht="99.95" customHeight="1">
-      <c r="A18" s="41"/>
-      <c r="B18" s="42"/>
-      <c r="C18" s="43" t="s">
+      <c r="H17" s="41"/>
+    </row>
+    <row r="18" spans="1:8" s="40" customFormat="1" ht="99.95" customHeight="1">
+      <c r="A18" s="37"/>
+      <c r="B18" s="38"/>
+      <c r="C18" s="39" t="s">
         <v>153</v>
       </c>
-      <c r="D18" s="43" t="s">
+      <c r="D18" s="39" t="s">
         <v>154</v>
       </c>
-      <c r="E18" s="43" t="s">
+      <c r="E18" s="39" t="s">
         <v>155</v>
       </c>
-      <c r="F18" s="43" t="s">
+      <c r="F18" s="39" t="s">
         <v>156</v>
       </c>
-      <c r="G18" s="41" t="s">
+      <c r="G18" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="H18" s="45"/>
+      <c r="H18" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1720,13 +1870,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="15.75" customHeight="1">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
@@ -1734,13 +1884,13 @@
       <c r="J1" s="6"/>
     </row>
     <row r="2" spans="1:27" ht="15.75" customHeight="1">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
@@ -2589,7 +2739,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="9"/>
-      <c r="C23" s="49" t="s">
+      <c r="C23" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D23" s="9" t="s">
@@ -2632,7 +2782,7 @@
         <v>20</v>
       </c>
       <c r="B24" s="14"/>
-      <c r="C24" s="49" t="s">
+      <c r="C24" s="45" t="s">
         <v>103</v>
       </c>
       <c r="D24" s="14" t="s">
@@ -2947,995 +3097,1395 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AA29"/>
+  <dimension ref="A1:AA50"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" style="55" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" style="52"/>
-    <col min="3" max="3" width="20.7109375" style="55" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" style="55" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" style="52" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="55" customWidth="1"/>
-    <col min="7" max="7" width="44.140625" style="55" customWidth="1"/>
-    <col min="8" max="8" width="51.85546875" style="63" customWidth="1"/>
-    <col min="9" max="9" width="26.85546875" style="52" customWidth="1"/>
-    <col min="10" max="10" width="20" style="52" customWidth="1"/>
-    <col min="11" max="16384" width="12.5703125" style="52"/>
+    <col min="1" max="1" width="7.28515625" style="18" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" style="50"/>
+    <col min="3" max="3" width="20.7109375" style="18" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" style="18" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" style="50" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="18" customWidth="1"/>
+    <col min="7" max="7" width="44.140625" style="18" customWidth="1"/>
+    <col min="8" max="8" width="51.85546875" style="68" customWidth="1"/>
+    <col min="9" max="9" width="26.85546875" style="50" customWidth="1"/>
+    <col min="10" max="10" width="20" style="50" customWidth="1"/>
+    <col min="11" max="16384" width="12.5703125" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="15.75" customHeight="1">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="58" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
     </row>
     <row r="2" spans="1:27" ht="15.75" customHeight="1">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
     </row>
     <row r="3" spans="1:27" ht="15.75" customHeight="1">
-      <c r="A3" s="51"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
+      <c r="A3" s="46"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
     </row>
     <row r="4" spans="1:27" ht="15.75" customHeight="1">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="53" t="s">
+      <c r="B4" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="53" t="s">
+      <c r="D4" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="53" t="s">
+      <c r="E4" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="53" t="s">
+      <c r="F4" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="53" t="s">
+      <c r="G4" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="61" t="s">
+      <c r="H4" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="I4" s="53" t="s">
+      <c r="I4" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="J4" s="53" t="s">
+      <c r="J4" s="65" t="s">
         <v>51</v>
       </c>
-      <c r="K4" s="54"/>
-      <c r="L4" s="54"/>
-      <c r="M4" s="54"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="54"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="54"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="54"/>
-      <c r="T4" s="54"/>
-      <c r="U4" s="54"/>
-      <c r="V4" s="54"/>
-      <c r="W4" s="54"/>
-      <c r="X4" s="54"/>
-      <c r="Y4" s="54"/>
-      <c r="Z4" s="54"/>
-      <c r="AA4" s="54"/>
-    </row>
-    <row r="5" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A5" s="32"/>
-      <c r="B5" s="56"/>
-      <c r="C5" s="32" t="s">
+      <c r="K4" s="49"/>
+      <c r="L4" s="49"/>
+      <c r="M4" s="49"/>
+      <c r="N4" s="49"/>
+      <c r="O4" s="49"/>
+      <c r="P4" s="49"/>
+      <c r="Q4" s="49"/>
+      <c r="R4" s="49"/>
+      <c r="S4" s="49"/>
+      <c r="T4" s="49"/>
+      <c r="U4" s="49"/>
+      <c r="V4" s="49"/>
+      <c r="W4" s="49"/>
+      <c r="X4" s="49"/>
+      <c r="Y4" s="49"/>
+      <c r="Z4" s="49"/>
+      <c r="AA4" s="49"/>
+    </row>
+    <row r="5" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A5" s="28"/>
+      <c r="B5" s="47"/>
+      <c r="C5" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="D5" s="32" t="s">
+      <c r="D5" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="56"/>
-      <c r="F5" s="32" t="s">
+      <c r="E5" s="47"/>
+      <c r="F5" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="G5" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="H5" s="62" t="s">
+      <c r="H5" s="52" t="s">
         <v>161</v>
       </c>
-      <c r="I5" s="57"/>
-      <c r="J5" s="56"/>
-      <c r="K5" s="58"/>
-      <c r="L5" s="58"/>
-      <c r="M5" s="58"/>
-      <c r="N5" s="58"/>
-      <c r="O5" s="58"/>
-      <c r="P5" s="58"/>
-      <c r="Q5" s="58"/>
-      <c r="R5" s="58"/>
-      <c r="S5" s="58"/>
-      <c r="T5" s="58"/>
-      <c r="U5" s="58"/>
-      <c r="V5" s="58"/>
-      <c r="W5" s="58"/>
-      <c r="X5" s="58"/>
-      <c r="Y5" s="58"/>
-      <c r="Z5" s="58"/>
-      <c r="AA5" s="58"/>
-    </row>
-    <row r="6" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A6" s="32"/>
-      <c r="B6" s="56"/>
-      <c r="C6" s="32" t="s">
+      <c r="I5" s="48"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="49"/>
+      <c r="L5" s="49"/>
+      <c r="M5" s="49"/>
+      <c r="N5" s="49"/>
+      <c r="O5" s="49"/>
+      <c r="P5" s="49"/>
+      <c r="Q5" s="49"/>
+      <c r="R5" s="49"/>
+      <c r="S5" s="49"/>
+      <c r="T5" s="49"/>
+      <c r="U5" s="49"/>
+      <c r="V5" s="49"/>
+      <c r="W5" s="49"/>
+      <c r="X5" s="49"/>
+      <c r="Y5" s="49"/>
+      <c r="Z5" s="49"/>
+      <c r="AA5" s="49"/>
+    </row>
+    <row r="6" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A6" s="28"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="D6" s="32" t="s">
+      <c r="D6" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="E6" s="56"/>
-      <c r="F6" s="32" t="s">
+      <c r="E6" s="47"/>
+      <c r="F6" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="H6" s="62" t="s">
+      <c r="H6" s="52" t="s">
         <v>163</v>
       </c>
-      <c r="I6" s="56"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="58"/>
-      <c r="M6" s="58"/>
-      <c r="N6" s="58"/>
-      <c r="O6" s="58"/>
-      <c r="P6" s="58"/>
-      <c r="Q6" s="58"/>
-      <c r="R6" s="58"/>
-      <c r="S6" s="58"/>
-      <c r="T6" s="58"/>
-      <c r="U6" s="58"/>
-      <c r="V6" s="58"/>
-      <c r="W6" s="58"/>
-      <c r="X6" s="58"/>
-      <c r="Y6" s="58"/>
-      <c r="Z6" s="58"/>
-      <c r="AA6" s="58"/>
-    </row>
-    <row r="7" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A7" s="32"/>
-      <c r="B7" s="56"/>
-      <c r="C7" s="32" t="s">
+      <c r="I6" s="47"/>
+      <c r="J6" s="47"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="49"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="49"/>
+      <c r="P6" s="49"/>
+      <c r="Q6" s="49"/>
+      <c r="R6" s="49"/>
+      <c r="S6" s="49"/>
+      <c r="T6" s="49"/>
+      <c r="U6" s="49"/>
+      <c r="V6" s="49"/>
+      <c r="W6" s="49"/>
+      <c r="X6" s="49"/>
+      <c r="Y6" s="49"/>
+      <c r="Z6" s="49"/>
+      <c r="AA6" s="49"/>
+    </row>
+    <row r="7" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A7" s="28"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="D7" s="32" t="s">
+      <c r="D7" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="56"/>
-      <c r="F7" s="32" t="s">
+      <c r="E7" s="47"/>
+      <c r="F7" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="G7" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="H7" s="62" t="s">
+      <c r="H7" s="52" t="s">
         <v>163</v>
       </c>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="58"/>
-      <c r="L7" s="58"/>
-      <c r="M7" s="58"/>
-      <c r="N7" s="58"/>
-      <c r="O7" s="58"/>
-      <c r="P7" s="58"/>
-      <c r="Q7" s="58"/>
-      <c r="R7" s="58"/>
-      <c r="S7" s="58"/>
-      <c r="T7" s="58"/>
-      <c r="U7" s="58"/>
-      <c r="V7" s="58"/>
-      <c r="W7" s="58"/>
-      <c r="X7" s="58"/>
-      <c r="Y7" s="58"/>
-      <c r="Z7" s="58"/>
-      <c r="AA7" s="58"/>
-    </row>
-    <row r="8" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A8" s="32"/>
-      <c r="B8" s="56"/>
-      <c r="C8" s="32" t="s">
+      <c r="I7" s="47"/>
+      <c r="J7" s="47"/>
+      <c r="K7" s="49"/>
+      <c r="L7" s="49"/>
+      <c r="M7" s="49"/>
+      <c r="N7" s="49"/>
+      <c r="O7" s="49"/>
+      <c r="P7" s="49"/>
+      <c r="Q7" s="49"/>
+      <c r="R7" s="49"/>
+      <c r="S7" s="49"/>
+      <c r="T7" s="49"/>
+      <c r="U7" s="49"/>
+      <c r="V7" s="49"/>
+      <c r="W7" s="49"/>
+      <c r="X7" s="49"/>
+      <c r="Y7" s="49"/>
+      <c r="Z7" s="49"/>
+      <c r="AA7" s="49"/>
+    </row>
+    <row r="8" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A8" s="28"/>
+      <c r="B8" s="47"/>
+      <c r="C8" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="56"/>
-      <c r="F8" s="32" t="s">
+      <c r="E8" s="47"/>
+      <c r="F8" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="G8" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="H8" s="62" t="s">
+      <c r="H8" s="52" t="s">
         <v>166</v>
       </c>
-      <c r="I8" s="56"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="58"/>
-      <c r="L8" s="58"/>
-      <c r="M8" s="58"/>
-      <c r="N8" s="58"/>
-      <c r="O8" s="58"/>
-      <c r="P8" s="58"/>
-      <c r="Q8" s="58"/>
-      <c r="R8" s="58"/>
-      <c r="S8" s="58"/>
-      <c r="T8" s="58"/>
-      <c r="U8" s="58"/>
-      <c r="V8" s="58"/>
-      <c r="W8" s="58"/>
-      <c r="X8" s="58"/>
-      <c r="Y8" s="58"/>
-      <c r="Z8" s="58"/>
-      <c r="AA8" s="58"/>
-    </row>
-    <row r="9" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A9" s="32"/>
-      <c r="B9" s="56"/>
-      <c r="C9" s="32" t="s">
+      <c r="I8" s="47"/>
+      <c r="J8" s="47"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49"/>
+      <c r="N8" s="49"/>
+      <c r="O8" s="49"/>
+      <c r="P8" s="49"/>
+      <c r="Q8" s="49"/>
+      <c r="R8" s="49"/>
+      <c r="S8" s="49"/>
+      <c r="T8" s="49"/>
+      <c r="U8" s="49"/>
+      <c r="V8" s="49"/>
+      <c r="W8" s="49"/>
+      <c r="X8" s="49"/>
+      <c r="Y8" s="49"/>
+      <c r="Z8" s="49"/>
+      <c r="AA8" s="49"/>
+    </row>
+    <row r="9" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A9" s="28"/>
+      <c r="B9" s="47"/>
+      <c r="C9" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="D9" s="32" t="s">
+      <c r="D9" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="E9" s="56"/>
-      <c r="F9" s="32" t="s">
+      <c r="E9" s="47"/>
+      <c r="F9" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="G9" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="H9" s="62" t="s">
+      <c r="H9" s="52" t="s">
         <v>168</v>
       </c>
-      <c r="I9" s="56"/>
-      <c r="J9" s="56"/>
-      <c r="K9" s="58"/>
-      <c r="L9" s="58"/>
-      <c r="M9" s="58"/>
-      <c r="N9" s="58"/>
-      <c r="O9" s="58"/>
-      <c r="P9" s="58"/>
-      <c r="Q9" s="58"/>
-      <c r="R9" s="58"/>
-      <c r="S9" s="58"/>
-      <c r="T9" s="58"/>
-      <c r="U9" s="58"/>
-      <c r="V9" s="58"/>
-      <c r="W9" s="58"/>
-      <c r="X9" s="58"/>
-      <c r="Y9" s="58"/>
-      <c r="Z9" s="58"/>
-      <c r="AA9" s="58"/>
-    </row>
-    <row r="10" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A10" s="32"/>
-      <c r="B10" s="56"/>
-      <c r="C10" s="32" t="s">
+      <c r="I9" s="47"/>
+      <c r="J9" s="47"/>
+      <c r="K9" s="49"/>
+      <c r="L9" s="49"/>
+      <c r="M9" s="49"/>
+      <c r="N9" s="49"/>
+      <c r="O9" s="49"/>
+      <c r="P9" s="49"/>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="49"/>
+      <c r="S9" s="49"/>
+      <c r="T9" s="49"/>
+      <c r="U9" s="49"/>
+      <c r="V9" s="49"/>
+      <c r="W9" s="49"/>
+      <c r="X9" s="49"/>
+      <c r="Y9" s="49"/>
+      <c r="Z9" s="49"/>
+      <c r="AA9" s="49"/>
+    </row>
+    <row r="10" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A10" s="28"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="56"/>
-      <c r="F10" s="32" t="s">
+      <c r="E10" s="47"/>
+      <c r="F10" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="G10" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="H10" s="62" t="s">
+      <c r="H10" s="52" t="s">
         <v>163</v>
       </c>
-      <c r="I10" s="56"/>
-      <c r="J10" s="56"/>
-      <c r="K10" s="58"/>
-      <c r="L10" s="58"/>
-      <c r="M10" s="58"/>
-      <c r="N10" s="58"/>
-      <c r="O10" s="58"/>
-      <c r="P10" s="58"/>
-      <c r="Q10" s="58"/>
-      <c r="R10" s="58"/>
-      <c r="S10" s="58"/>
-      <c r="T10" s="58"/>
-      <c r="U10" s="58"/>
-      <c r="V10" s="58"/>
-      <c r="W10" s="58"/>
-      <c r="X10" s="58"/>
-      <c r="Y10" s="58"/>
-      <c r="Z10" s="58"/>
-      <c r="AA10" s="58"/>
-    </row>
-    <row r="11" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A11" s="32"/>
-      <c r="B11" s="56"/>
-      <c r="C11" s="32" t="s">
+      <c r="I10" s="47"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="49"/>
+      <c r="N10" s="49"/>
+      <c r="O10" s="49"/>
+      <c r="P10" s="49"/>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="49"/>
+      <c r="S10" s="49"/>
+      <c r="T10" s="49"/>
+      <c r="U10" s="49"/>
+      <c r="V10" s="49"/>
+      <c r="W10" s="49"/>
+      <c r="X10" s="49"/>
+      <c r="Y10" s="49"/>
+      <c r="Z10" s="49"/>
+      <c r="AA10" s="49"/>
+    </row>
+    <row r="11" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A11" s="28"/>
+      <c r="B11" s="47"/>
+      <c r="C11" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="D11" s="32" t="s">
+      <c r="D11" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="56"/>
-      <c r="F11" s="32" t="s">
+      <c r="E11" s="47"/>
+      <c r="F11" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="G11" s="32" t="s">
+      <c r="G11" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="H11" s="62" t="s">
+      <c r="H11" s="52" t="s">
         <v>163</v>
       </c>
-      <c r="I11" s="56"/>
-      <c r="J11" s="56"/>
-      <c r="K11" s="58"/>
-      <c r="L11" s="58"/>
-      <c r="M11" s="58"/>
-      <c r="N11" s="58"/>
-      <c r="O11" s="58"/>
-      <c r="P11" s="58"/>
-      <c r="Q11" s="58"/>
-      <c r="R11" s="58"/>
-      <c r="S11" s="58"/>
-      <c r="T11" s="58"/>
-      <c r="U11" s="58"/>
-      <c r="V11" s="58"/>
-      <c r="W11" s="58"/>
-      <c r="X11" s="58"/>
-      <c r="Y11" s="58"/>
-      <c r="Z11" s="58"/>
-      <c r="AA11" s="58"/>
-    </row>
-    <row r="12" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A12" s="32"/>
-      <c r="B12" s="56"/>
-      <c r="C12" s="32" t="s">
+      <c r="I11" s="47"/>
+      <c r="J11" s="47"/>
+      <c r="K11" s="49"/>
+      <c r="L11" s="49"/>
+      <c r="M11" s="49"/>
+      <c r="N11" s="49"/>
+      <c r="O11" s="49"/>
+      <c r="P11" s="49"/>
+      <c r="Q11" s="49"/>
+      <c r="R11" s="49"/>
+      <c r="S11" s="49"/>
+      <c r="T11" s="49"/>
+      <c r="U11" s="49"/>
+      <c r="V11" s="49"/>
+      <c r="W11" s="49"/>
+      <c r="X11" s="49"/>
+      <c r="Y11" s="49"/>
+      <c r="Z11" s="49"/>
+      <c r="AA11" s="49"/>
+    </row>
+    <row r="12" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A12" s="28"/>
+      <c r="B12" s="47"/>
+      <c r="C12" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="E12" s="56"/>
-      <c r="F12" s="32" t="s">
+      <c r="E12" s="47"/>
+      <c r="F12" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="G12" s="32" t="s">
+      <c r="G12" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="H12" s="64" t="s">
+      <c r="H12" s="53" t="s">
         <v>174</v>
       </c>
-      <c r="I12" s="56"/>
-      <c r="J12" s="56"/>
-      <c r="K12" s="58"/>
-      <c r="L12" s="58"/>
-      <c r="M12" s="58"/>
-      <c r="N12" s="58"/>
-      <c r="O12" s="58"/>
-      <c r="P12" s="58"/>
-      <c r="Q12" s="58"/>
-      <c r="R12" s="58"/>
-      <c r="S12" s="58"/>
-      <c r="T12" s="58"/>
-      <c r="U12" s="58"/>
-      <c r="V12" s="58"/>
-      <c r="W12" s="58"/>
-      <c r="X12" s="58"/>
-      <c r="Y12" s="58"/>
-      <c r="Z12" s="58"/>
-      <c r="AA12" s="58"/>
-    </row>
-    <row r="13" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A13" s="32"/>
-      <c r="B13" s="56"/>
-      <c r="C13" s="32" t="s">
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="49"/>
+      <c r="L12" s="49"/>
+      <c r="M12" s="49"/>
+      <c r="N12" s="49"/>
+      <c r="O12" s="49"/>
+      <c r="P12" s="49"/>
+      <c r="Q12" s="49"/>
+      <c r="R12" s="49"/>
+      <c r="S12" s="49"/>
+      <c r="T12" s="49"/>
+      <c r="U12" s="49"/>
+      <c r="V12" s="49"/>
+      <c r="W12" s="49"/>
+      <c r="X12" s="49"/>
+      <c r="Y12" s="49"/>
+      <c r="Z12" s="49"/>
+      <c r="AA12" s="49"/>
+    </row>
+    <row r="13" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A13" s="28"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="E13" s="56"/>
-      <c r="F13" s="32" t="s">
+      <c r="E13" s="47"/>
+      <c r="F13" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="H13" s="62" t="s">
+      <c r="H13" s="52" t="s">
         <v>176</v>
       </c>
-      <c r="I13" s="56"/>
-      <c r="J13" s="56"/>
-      <c r="K13" s="58"/>
-      <c r="L13" s="58"/>
-      <c r="M13" s="58"/>
-      <c r="N13" s="58"/>
-      <c r="O13" s="58"/>
-      <c r="P13" s="58"/>
-      <c r="Q13" s="58"/>
-      <c r="R13" s="58"/>
-      <c r="S13" s="58"/>
-      <c r="T13" s="58"/>
-      <c r="U13" s="58"/>
-      <c r="V13" s="58"/>
-      <c r="W13" s="58"/>
-      <c r="X13" s="58"/>
-      <c r="Y13" s="58"/>
-      <c r="Z13" s="58"/>
-      <c r="AA13" s="58"/>
-    </row>
-    <row r="14" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A14" s="32"/>
-      <c r="B14" s="56"/>
-      <c r="C14" s="32" t="s">
+      <c r="I13" s="47"/>
+      <c r="J13" s="47"/>
+      <c r="K13" s="49"/>
+      <c r="L13" s="49"/>
+      <c r="M13" s="49"/>
+      <c r="N13" s="49"/>
+      <c r="O13" s="49"/>
+      <c r="P13" s="49"/>
+      <c r="Q13" s="49"/>
+      <c r="R13" s="49"/>
+      <c r="S13" s="49"/>
+      <c r="T13" s="49"/>
+      <c r="U13" s="49"/>
+      <c r="V13" s="49"/>
+      <c r="W13" s="49"/>
+      <c r="X13" s="49"/>
+      <c r="Y13" s="49"/>
+      <c r="Z13" s="49"/>
+      <c r="AA13" s="49"/>
+    </row>
+    <row r="14" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A14" s="28"/>
+      <c r="B14" s="47"/>
+      <c r="C14" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="E14" s="56"/>
-      <c r="F14" s="32" t="s">
+      <c r="E14" s="47"/>
+      <c r="F14" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="H14" s="62" t="s">
+      <c r="H14" s="52" t="s">
         <v>178</v>
       </c>
-      <c r="I14" s="56"/>
-      <c r="J14" s="56"/>
-      <c r="K14" s="58"/>
-      <c r="L14" s="58"/>
-      <c r="M14" s="58"/>
-      <c r="N14" s="58"/>
-      <c r="O14" s="58"/>
-      <c r="P14" s="58"/>
-      <c r="Q14" s="58"/>
-      <c r="R14" s="58"/>
-      <c r="S14" s="58"/>
-      <c r="T14" s="58"/>
-      <c r="U14" s="58"/>
-      <c r="V14" s="58"/>
-      <c r="W14" s="58"/>
-      <c r="X14" s="58"/>
-      <c r="Y14" s="58"/>
-      <c r="Z14" s="58"/>
-      <c r="AA14" s="58"/>
-    </row>
-    <row r="15" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A15" s="32"/>
-      <c r="B15" s="56"/>
-      <c r="C15" s="32" t="s">
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="49"/>
+      <c r="L14" s="49"/>
+      <c r="M14" s="49"/>
+      <c r="N14" s="49"/>
+      <c r="O14" s="49"/>
+      <c r="P14" s="49"/>
+      <c r="Q14" s="49"/>
+      <c r="R14" s="49"/>
+      <c r="S14" s="49"/>
+      <c r="T14" s="49"/>
+      <c r="U14" s="49"/>
+      <c r="V14" s="49"/>
+      <c r="W14" s="49"/>
+      <c r="X14" s="49"/>
+      <c r="Y14" s="49"/>
+      <c r="Z14" s="49"/>
+      <c r="AA14" s="49"/>
+    </row>
+    <row r="15" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A15" s="28"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="E15" s="56"/>
-      <c r="F15" s="32" t="s">
+      <c r="E15" s="47"/>
+      <c r="F15" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="32" t="s">
+      <c r="G15" s="28" t="s">
         <v>179</v>
       </c>
-      <c r="H15" s="64" t="s">
+      <c r="H15" s="53" t="s">
         <v>180</v>
       </c>
-      <c r="I15" s="56"/>
-      <c r="J15" s="56"/>
-      <c r="K15" s="58"/>
-      <c r="L15" s="58"/>
-      <c r="M15" s="58"/>
-      <c r="N15" s="58"/>
-      <c r="O15" s="58"/>
-      <c r="P15" s="58"/>
-      <c r="Q15" s="58"/>
-      <c r="R15" s="58"/>
-      <c r="S15" s="58"/>
-      <c r="T15" s="58"/>
-      <c r="U15" s="58"/>
-      <c r="V15" s="58"/>
-      <c r="W15" s="58"/>
-      <c r="X15" s="58"/>
-      <c r="Y15" s="58"/>
-      <c r="Z15" s="58"/>
-      <c r="AA15" s="58"/>
-    </row>
-    <row r="16" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A16" s="32"/>
-      <c r="B16" s="56"/>
-      <c r="C16" s="32" t="s">
+      <c r="I15" s="47"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="49"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="49"/>
+      <c r="N15" s="49"/>
+      <c r="O15" s="49"/>
+      <c r="P15" s="49"/>
+      <c r="Q15" s="49"/>
+      <c r="R15" s="49"/>
+      <c r="S15" s="49"/>
+      <c r="T15" s="49"/>
+      <c r="U15" s="49"/>
+      <c r="V15" s="49"/>
+      <c r="W15" s="49"/>
+      <c r="X15" s="49"/>
+      <c r="Y15" s="49"/>
+      <c r="Z15" s="49"/>
+      <c r="AA15" s="49"/>
+    </row>
+    <row r="16" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A16" s="28"/>
+      <c r="B16" s="47"/>
+      <c r="C16" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="E16" s="56"/>
-      <c r="F16" s="32" t="s">
+      <c r="E16" s="47"/>
+      <c r="F16" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="G16" s="32" t="s">
+      <c r="G16" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="H16" s="62" t="s">
+      <c r="H16" s="52" t="s">
         <v>182</v>
       </c>
-      <c r="I16" s="56"/>
-      <c r="J16" s="56"/>
-      <c r="K16" s="58"/>
-      <c r="L16" s="58"/>
-      <c r="M16" s="58"/>
-      <c r="N16" s="58"/>
-      <c r="O16" s="58"/>
-      <c r="P16" s="58"/>
-      <c r="Q16" s="58"/>
-      <c r="R16" s="58"/>
-      <c r="S16" s="58"/>
-      <c r="T16" s="58"/>
-      <c r="U16" s="58"/>
-      <c r="V16" s="58"/>
-      <c r="W16" s="58"/>
-      <c r="X16" s="58"/>
-      <c r="Y16" s="58"/>
-      <c r="Z16" s="58"/>
-      <c r="AA16" s="58"/>
-    </row>
-    <row r="17" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A17" s="32"/>
-      <c r="B17" s="56"/>
-      <c r="C17" s="32" t="s">
+      <c r="I16" s="47"/>
+      <c r="J16" s="47"/>
+      <c r="K16" s="49"/>
+      <c r="L16" s="49"/>
+      <c r="M16" s="49"/>
+      <c r="N16" s="49"/>
+      <c r="O16" s="49"/>
+      <c r="P16" s="49"/>
+      <c r="Q16" s="49"/>
+      <c r="R16" s="49"/>
+      <c r="S16" s="49"/>
+      <c r="T16" s="49"/>
+      <c r="U16" s="49"/>
+      <c r="V16" s="49"/>
+      <c r="W16" s="49"/>
+      <c r="X16" s="49"/>
+      <c r="Y16" s="49"/>
+      <c r="Z16" s="49"/>
+      <c r="AA16" s="49"/>
+    </row>
+    <row r="17" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A17" s="28"/>
+      <c r="B17" s="47"/>
+      <c r="C17" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="E17" s="56"/>
-      <c r="F17" s="32" t="s">
+      <c r="E17" s="47"/>
+      <c r="F17" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="G17" s="32" t="s">
+      <c r="G17" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="H17" s="62" t="s">
+      <c r="H17" s="52" t="s">
         <v>184</v>
       </c>
-      <c r="I17" s="56"/>
-      <c r="J17" s="56"/>
-      <c r="K17" s="58"/>
-      <c r="L17" s="58"/>
-      <c r="M17" s="58"/>
-      <c r="N17" s="58"/>
-      <c r="O17" s="58"/>
-      <c r="P17" s="58"/>
-      <c r="Q17" s="58"/>
-      <c r="R17" s="58"/>
-      <c r="S17" s="58"/>
-      <c r="T17" s="58"/>
-      <c r="U17" s="58"/>
-      <c r="V17" s="58"/>
-      <c r="W17" s="58"/>
-      <c r="X17" s="58"/>
-      <c r="Y17" s="58"/>
-      <c r="Z17" s="58"/>
-      <c r="AA17" s="58"/>
-    </row>
-    <row r="18" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A18" s="32"/>
-      <c r="B18" s="56"/>
-      <c r="C18" s="32" t="s">
+      <c r="I17" s="47"/>
+      <c r="J17" s="47"/>
+      <c r="K17" s="49"/>
+      <c r="L17" s="49"/>
+      <c r="M17" s="49"/>
+      <c r="N17" s="49"/>
+      <c r="O17" s="49"/>
+      <c r="P17" s="49"/>
+      <c r="Q17" s="49"/>
+      <c r="R17" s="49"/>
+      <c r="S17" s="49"/>
+      <c r="T17" s="49"/>
+      <c r="U17" s="49"/>
+      <c r="V17" s="49"/>
+      <c r="W17" s="49"/>
+      <c r="X17" s="49"/>
+      <c r="Y17" s="49"/>
+      <c r="Z17" s="49"/>
+      <c r="AA17" s="49"/>
+    </row>
+    <row r="18" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A18" s="28"/>
+      <c r="B18" s="47"/>
+      <c r="C18" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="E18" s="56"/>
-      <c r="F18" s="32" t="s">
+      <c r="E18" s="47"/>
+      <c r="F18" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="G18" s="32" t="s">
+      <c r="G18" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="H18" s="62" t="s">
+      <c r="H18" s="52" t="s">
         <v>186</v>
       </c>
-      <c r="I18" s="56"/>
-      <c r="J18" s="56"/>
-      <c r="K18" s="58"/>
-      <c r="L18" s="58"/>
-      <c r="M18" s="58"/>
-      <c r="N18" s="58"/>
-      <c r="O18" s="58"/>
-      <c r="P18" s="58"/>
-      <c r="Q18" s="58"/>
-      <c r="R18" s="58"/>
-      <c r="S18" s="58"/>
-      <c r="T18" s="58"/>
-      <c r="U18" s="58"/>
-      <c r="V18" s="58"/>
-      <c r="W18" s="58"/>
-      <c r="X18" s="58"/>
-      <c r="Y18" s="58"/>
-      <c r="Z18" s="58"/>
-      <c r="AA18" s="58"/>
-    </row>
-    <row r="19" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A19" s="32"/>
-      <c r="B19" s="56"/>
-      <c r="C19" s="32" t="s">
+      <c r="I18" s="47"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="49"/>
+      <c r="L18" s="49"/>
+      <c r="M18" s="49"/>
+      <c r="N18" s="49"/>
+      <c r="O18" s="49"/>
+      <c r="P18" s="49"/>
+      <c r="Q18" s="49"/>
+      <c r="R18" s="49"/>
+      <c r="S18" s="49"/>
+      <c r="T18" s="49"/>
+      <c r="U18" s="49"/>
+      <c r="V18" s="49"/>
+      <c r="W18" s="49"/>
+      <c r="X18" s="49"/>
+      <c r="Y18" s="49"/>
+      <c r="Z18" s="49"/>
+      <c r="AA18" s="49"/>
+    </row>
+    <row r="19" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A19" s="28"/>
+      <c r="B19" s="47"/>
+      <c r="C19" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="E19" s="56"/>
-      <c r="F19" s="32" t="s">
+      <c r="E19" s="47"/>
+      <c r="F19" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="G19" s="32" t="s">
+      <c r="G19" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="H19" s="62" t="s">
+      <c r="H19" s="52" t="s">
         <v>188</v>
       </c>
-      <c r="I19" s="56"/>
-      <c r="J19" s="56"/>
-      <c r="K19" s="58"/>
-      <c r="L19" s="58"/>
-      <c r="M19" s="58"/>
-      <c r="N19" s="58"/>
-      <c r="O19" s="58"/>
-      <c r="P19" s="58"/>
-      <c r="Q19" s="58"/>
-      <c r="R19" s="58"/>
-      <c r="S19" s="58"/>
-      <c r="T19" s="58"/>
-      <c r="U19" s="58"/>
-      <c r="V19" s="58"/>
-      <c r="W19" s="58"/>
-      <c r="X19" s="58"/>
-      <c r="Y19" s="58"/>
-      <c r="Z19" s="58"/>
-      <c r="AA19" s="58"/>
-    </row>
-    <row r="20" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A20" s="32"/>
-      <c r="B20" s="56"/>
-      <c r="C20" s="32" t="s">
+      <c r="I19" s="47"/>
+      <c r="J19" s="47"/>
+      <c r="K19" s="49"/>
+      <c r="L19" s="49"/>
+      <c r="M19" s="49"/>
+      <c r="N19" s="49"/>
+      <c r="O19" s="49"/>
+      <c r="P19" s="49"/>
+      <c r="Q19" s="49"/>
+      <c r="R19" s="49"/>
+      <c r="S19" s="49"/>
+      <c r="T19" s="49"/>
+      <c r="U19" s="49"/>
+      <c r="V19" s="49"/>
+      <c r="W19" s="49"/>
+      <c r="X19" s="49"/>
+      <c r="Y19" s="49"/>
+      <c r="Z19" s="49"/>
+      <c r="AA19" s="49"/>
+    </row>
+    <row r="20" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A20" s="28"/>
+      <c r="B20" s="47"/>
+      <c r="C20" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="E20" s="56"/>
-      <c r="F20" s="32" t="s">
+      <c r="E20" s="47"/>
+      <c r="F20" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="G20" s="32" t="s">
+      <c r="G20" s="28" t="s">
         <v>189</v>
       </c>
-      <c r="H20" s="62" t="s">
+      <c r="H20" s="52" t="s">
         <v>190</v>
       </c>
-      <c r="I20" s="56"/>
-      <c r="J20" s="56"/>
-      <c r="K20" s="58"/>
-      <c r="L20" s="58"/>
-      <c r="M20" s="58"/>
-      <c r="N20" s="58"/>
-      <c r="O20" s="58"/>
-      <c r="P20" s="58"/>
-      <c r="Q20" s="58"/>
-      <c r="R20" s="58"/>
-      <c r="S20" s="58"/>
-      <c r="T20" s="58"/>
-      <c r="U20" s="58"/>
-      <c r="V20" s="58"/>
-      <c r="W20" s="58"/>
-      <c r="X20" s="58"/>
-      <c r="Y20" s="58"/>
-      <c r="Z20" s="58"/>
-      <c r="AA20" s="58"/>
-    </row>
-    <row r="21" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A21" s="32"/>
-      <c r="B21" s="56"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="62"/>
-      <c r="I21" s="56"/>
-      <c r="J21" s="56"/>
-      <c r="K21" s="58"/>
-      <c r="L21" s="58"/>
-      <c r="M21" s="58"/>
-      <c r="N21" s="58"/>
-      <c r="O21" s="58"/>
-      <c r="P21" s="58"/>
-      <c r="Q21" s="58"/>
-      <c r="R21" s="58"/>
-      <c r="S21" s="58"/>
-      <c r="T21" s="58"/>
-      <c r="U21" s="58"/>
-      <c r="V21" s="58"/>
-      <c r="W21" s="58"/>
-      <c r="X21" s="58"/>
-      <c r="Y21" s="58"/>
-      <c r="Z21" s="58"/>
-      <c r="AA21" s="58"/>
-    </row>
-    <row r="22" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A22" s="32"/>
-      <c r="B22" s="56"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="56"/>
-      <c r="J22" s="56"/>
-      <c r="K22" s="58"/>
-      <c r="L22" s="58"/>
-      <c r="M22" s="58"/>
-      <c r="N22" s="58"/>
-      <c r="O22" s="58"/>
-      <c r="P22" s="58"/>
-      <c r="Q22" s="58"/>
-      <c r="R22" s="58"/>
-      <c r="S22" s="58"/>
-      <c r="T22" s="58"/>
-      <c r="U22" s="58"/>
-      <c r="V22" s="58"/>
-      <c r="W22" s="58"/>
-      <c r="X22" s="58"/>
-      <c r="Y22" s="58"/>
-      <c r="Z22" s="58"/>
-      <c r="AA22" s="58"/>
-    </row>
-    <row r="23" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A23" s="32"/>
-      <c r="B23" s="56"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="32"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="62"/>
-      <c r="I23" s="56"/>
-      <c r="J23" s="56"/>
-      <c r="K23" s="58"/>
-      <c r="L23" s="58"/>
-      <c r="M23" s="58"/>
-      <c r="N23" s="58"/>
-      <c r="O23" s="58"/>
-      <c r="P23" s="58"/>
-      <c r="Q23" s="58"/>
-      <c r="R23" s="58"/>
-      <c r="S23" s="58"/>
-      <c r="T23" s="58"/>
-      <c r="U23" s="58"/>
-      <c r="V23" s="58"/>
-      <c r="W23" s="58"/>
-      <c r="X23" s="58"/>
-      <c r="Y23" s="58"/>
-      <c r="Z23" s="58"/>
-      <c r="AA23" s="58"/>
-    </row>
-    <row r="24" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A24" s="32"/>
-      <c r="B24" s="56"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="56"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="62"/>
-      <c r="I24" s="56"/>
-      <c r="J24" s="56"/>
-      <c r="K24" s="58"/>
-      <c r="L24" s="58"/>
-      <c r="M24" s="58"/>
-      <c r="N24" s="58"/>
-      <c r="O24" s="58"/>
-      <c r="P24" s="58"/>
-      <c r="Q24" s="58"/>
-      <c r="R24" s="58"/>
-      <c r="S24" s="58"/>
-      <c r="T24" s="58"/>
-      <c r="U24" s="58"/>
-      <c r="V24" s="58"/>
-      <c r="W24" s="58"/>
-      <c r="X24" s="58"/>
-      <c r="Y24" s="58"/>
-      <c r="Z24" s="58"/>
-      <c r="AA24" s="58"/>
-    </row>
-    <row r="25" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A25" s="32"/>
-      <c r="B25" s="56"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="56"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="62"/>
-      <c r="I25" s="56"/>
-      <c r="J25" s="56"/>
-      <c r="K25" s="58"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="58"/>
-      <c r="N25" s="58"/>
-      <c r="O25" s="58"/>
-      <c r="P25" s="58"/>
-      <c r="Q25" s="58"/>
-      <c r="R25" s="58"/>
-      <c r="S25" s="58"/>
-      <c r="T25" s="58"/>
-      <c r="U25" s="58"/>
-      <c r="V25" s="58"/>
-      <c r="W25" s="58"/>
-      <c r="X25" s="58"/>
-      <c r="Y25" s="58"/>
-      <c r="Z25" s="58"/>
-      <c r="AA25" s="58"/>
-    </row>
-    <row r="26" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A26" s="32"/>
-      <c r="B26" s="56"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="62"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="56"/>
-      <c r="K26" s="58"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="58"/>
-      <c r="O26" s="58"/>
-      <c r="P26" s="58"/>
-      <c r="Q26" s="58"/>
-      <c r="R26" s="58"/>
-      <c r="S26" s="58"/>
-      <c r="T26" s="58"/>
-      <c r="U26" s="58"/>
-      <c r="V26" s="58"/>
-      <c r="W26" s="58"/>
-      <c r="X26" s="58"/>
-      <c r="Y26" s="58"/>
-      <c r="Z26" s="58"/>
-      <c r="AA26" s="58"/>
-    </row>
-    <row r="27" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A27" s="32"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="56"/>
-      <c r="K27" s="58"/>
-      <c r="L27" s="58"/>
-      <c r="M27" s="58"/>
-      <c r="N27" s="58"/>
-      <c r="O27" s="58"/>
-      <c r="P27" s="58"/>
-      <c r="Q27" s="58"/>
-      <c r="R27" s="58"/>
-      <c r="S27" s="58"/>
-      <c r="T27" s="58"/>
-      <c r="U27" s="58"/>
-      <c r="V27" s="58"/>
-      <c r="W27" s="58"/>
-      <c r="X27" s="58"/>
-      <c r="Y27" s="58"/>
-      <c r="Z27" s="58"/>
-      <c r="AA27" s="58"/>
-    </row>
-    <row r="28" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A28" s="32"/>
-      <c r="B28" s="56"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="62"/>
-      <c r="I28" s="56"/>
-      <c r="J28" s="56"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="58"/>
-      <c r="M28" s="58"/>
-      <c r="N28" s="58"/>
-      <c r="O28" s="58"/>
-      <c r="P28" s="58"/>
-      <c r="Q28" s="58"/>
-      <c r="R28" s="58"/>
-      <c r="S28" s="58"/>
-      <c r="T28" s="58"/>
-      <c r="U28" s="58"/>
-      <c r="V28" s="58"/>
-      <c r="W28" s="58"/>
-      <c r="X28" s="58"/>
-      <c r="Y28" s="58"/>
-      <c r="Z28" s="58"/>
-      <c r="AA28" s="58"/>
-    </row>
-    <row r="29" spans="1:27" s="59" customFormat="1" ht="50.1" customHeight="1">
-      <c r="A29" s="32"/>
-      <c r="B29" s="56"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="62"/>
-      <c r="I29" s="56"/>
-      <c r="J29" s="56"/>
-      <c r="K29" s="58"/>
-      <c r="L29" s="58"/>
-      <c r="M29" s="58"/>
-      <c r="N29" s="58"/>
-      <c r="O29" s="58"/>
-      <c r="P29" s="58"/>
-      <c r="Q29" s="58"/>
-      <c r="R29" s="58"/>
-      <c r="S29" s="58"/>
-      <c r="T29" s="58"/>
-      <c r="U29" s="58"/>
-      <c r="V29" s="58"/>
-      <c r="W29" s="58"/>
-      <c r="X29" s="58"/>
-      <c r="Y29" s="58"/>
-      <c r="Z29" s="58"/>
-      <c r="AA29" s="58"/>
+      <c r="I20" s="47"/>
+      <c r="J20" s="47"/>
+      <c r="K20" s="49"/>
+      <c r="L20" s="49"/>
+      <c r="M20" s="49"/>
+      <c r="N20" s="49"/>
+      <c r="O20" s="49"/>
+      <c r="P20" s="49"/>
+      <c r="Q20" s="49"/>
+      <c r="R20" s="49"/>
+      <c r="S20" s="49"/>
+      <c r="T20" s="49"/>
+      <c r="U20" s="49"/>
+      <c r="V20" s="49"/>
+      <c r="W20" s="49"/>
+      <c r="X20" s="49"/>
+      <c r="Y20" s="49"/>
+      <c r="Z20" s="49"/>
+      <c r="AA20" s="49"/>
+    </row>
+    <row r="21" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A21" s="28"/>
+      <c r="B21" s="47"/>
+      <c r="C21" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="D21" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="E21" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="F21" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="G21" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="H21" s="52" t="s">
+        <v>194</v>
+      </c>
+      <c r="I21" s="47"/>
+      <c r="J21" s="47"/>
+      <c r="K21" s="49"/>
+      <c r="L21" s="49"/>
+      <c r="M21" s="49"/>
+      <c r="N21" s="49"/>
+      <c r="O21" s="49"/>
+      <c r="P21" s="49"/>
+      <c r="Q21" s="49"/>
+      <c r="R21" s="49"/>
+      <c r="S21" s="49"/>
+      <c r="T21" s="49"/>
+      <c r="U21" s="49"/>
+      <c r="V21" s="49"/>
+      <c r="W21" s="49"/>
+      <c r="X21" s="49"/>
+      <c r="Y21" s="49"/>
+      <c r="Z21" s="49"/>
+      <c r="AA21" s="49"/>
+    </row>
+    <row r="22" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A22" s="28"/>
+      <c r="B22" s="47"/>
+      <c r="C22" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="D22" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="F22" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="G22" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="H22" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="I22" s="47"/>
+      <c r="J22" s="47"/>
+      <c r="K22" s="49"/>
+      <c r="L22" s="49"/>
+      <c r="M22" s="49"/>
+      <c r="N22" s="49"/>
+      <c r="O22" s="49"/>
+      <c r="P22" s="49"/>
+      <c r="Q22" s="49"/>
+      <c r="R22" s="49"/>
+      <c r="S22" s="49"/>
+      <c r="T22" s="49"/>
+      <c r="U22" s="49"/>
+      <c r="V22" s="49"/>
+      <c r="W22" s="49"/>
+      <c r="X22" s="49"/>
+      <c r="Y22" s="49"/>
+      <c r="Z22" s="49"/>
+      <c r="AA22" s="49"/>
+    </row>
+    <row r="23" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A23" s="28"/>
+      <c r="B23" s="47"/>
+      <c r="C23" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="F23" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="G23" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="H23" s="52" t="s">
+        <v>198</v>
+      </c>
+      <c r="I23" s="47"/>
+      <c r="J23" s="47"/>
+      <c r="K23" s="49"/>
+      <c r="L23" s="49"/>
+      <c r="M23" s="49"/>
+      <c r="N23" s="49"/>
+      <c r="O23" s="49"/>
+      <c r="P23" s="49"/>
+      <c r="Q23" s="49"/>
+      <c r="R23" s="49"/>
+      <c r="S23" s="49"/>
+      <c r="T23" s="49"/>
+      <c r="U23" s="49"/>
+      <c r="V23" s="49"/>
+      <c r="W23" s="49"/>
+      <c r="X23" s="49"/>
+      <c r="Y23" s="49"/>
+      <c r="Z23" s="49"/>
+      <c r="AA23" s="49"/>
+    </row>
+    <row r="24" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A24" s="28"/>
+      <c r="B24" s="47"/>
+      <c r="C24" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="D24" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="G24" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="H24" s="52" t="s">
+        <v>202</v>
+      </c>
+      <c r="I24" s="47"/>
+      <c r="J24" s="47"/>
+      <c r="K24" s="49"/>
+      <c r="L24" s="49"/>
+      <c r="M24" s="49"/>
+      <c r="N24" s="49"/>
+      <c r="O24" s="49"/>
+      <c r="P24" s="49"/>
+      <c r="Q24" s="49"/>
+      <c r="R24" s="49"/>
+      <c r="S24" s="49"/>
+      <c r="T24" s="49"/>
+      <c r="U24" s="49"/>
+      <c r="V24" s="49"/>
+      <c r="W24" s="49"/>
+      <c r="X24" s="49"/>
+      <c r="Y24" s="49"/>
+      <c r="Z24" s="49"/>
+      <c r="AA24" s="49"/>
+    </row>
+    <row r="25" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A25" s="28"/>
+      <c r="B25" s="47"/>
+      <c r="C25" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="D25" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="G25" s="28" t="s">
+        <v>203</v>
+      </c>
+      <c r="H25" s="52" t="s">
+        <v>204</v>
+      </c>
+      <c r="I25" s="47"/>
+      <c r="J25" s="47"/>
+      <c r="K25" s="49"/>
+      <c r="L25" s="49"/>
+      <c r="M25" s="49"/>
+      <c r="N25" s="49"/>
+      <c r="O25" s="49"/>
+      <c r="P25" s="49"/>
+      <c r="Q25" s="49"/>
+      <c r="R25" s="49"/>
+      <c r="S25" s="49"/>
+      <c r="T25" s="49"/>
+      <c r="U25" s="49"/>
+      <c r="V25" s="49"/>
+      <c r="W25" s="49"/>
+      <c r="X25" s="49"/>
+      <c r="Y25" s="49"/>
+      <c r="Z25" s="49"/>
+      <c r="AA25" s="49"/>
+    </row>
+    <row r="26" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A26" s="28"/>
+      <c r="B26" s="47"/>
+      <c r="C26" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="D26" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="E26" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="F26" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="G26" s="28" t="s">
+        <v>205</v>
+      </c>
+      <c r="H26" s="52" t="s">
+        <v>206</v>
+      </c>
+      <c r="I26" s="47"/>
+      <c r="J26" s="47"/>
+      <c r="K26" s="49"/>
+      <c r="L26" s="49"/>
+      <c r="M26" s="49"/>
+      <c r="N26" s="49"/>
+      <c r="O26" s="49"/>
+      <c r="P26" s="49"/>
+      <c r="Q26" s="49"/>
+      <c r="R26" s="49"/>
+      <c r="S26" s="49"/>
+      <c r="T26" s="49"/>
+      <c r="U26" s="49"/>
+      <c r="V26" s="49"/>
+      <c r="W26" s="49"/>
+      <c r="X26" s="49"/>
+      <c r="Y26" s="49"/>
+      <c r="Z26" s="49"/>
+      <c r="AA26" s="49"/>
+    </row>
+    <row r="27" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A27" s="28"/>
+      <c r="B27" s="47"/>
+      <c r="C27" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="E27" s="60"/>
+      <c r="F27" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="G27" s="28" t="s">
+        <v>207</v>
+      </c>
+      <c r="H27" s="52" t="s">
+        <v>208</v>
+      </c>
+      <c r="I27" s="47"/>
+      <c r="J27" s="47"/>
+      <c r="K27" s="49"/>
+      <c r="L27" s="49"/>
+      <c r="M27" s="49"/>
+      <c r="N27" s="49"/>
+      <c r="O27" s="49"/>
+      <c r="P27" s="49"/>
+      <c r="Q27" s="49"/>
+      <c r="R27" s="49"/>
+      <c r="S27" s="49"/>
+      <c r="T27" s="49"/>
+      <c r="U27" s="49"/>
+      <c r="V27" s="49"/>
+      <c r="W27" s="49"/>
+      <c r="X27" s="49"/>
+      <c r="Y27" s="49"/>
+      <c r="Z27" s="49"/>
+      <c r="AA27" s="49"/>
+    </row>
+    <row r="28" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A28" s="28"/>
+      <c r="B28" s="47"/>
+      <c r="C28" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="D28" s="28" t="s">
+        <v>214</v>
+      </c>
+      <c r="E28" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="F28" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="G28" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="H28" s="52" t="s">
+        <v>210</v>
+      </c>
+      <c r="I28" s="47"/>
+      <c r="J28" s="47"/>
+      <c r="K28" s="49"/>
+      <c r="L28" s="49"/>
+      <c r="M28" s="49"/>
+      <c r="N28" s="49"/>
+      <c r="O28" s="49"/>
+      <c r="P28" s="49"/>
+      <c r="Q28" s="49"/>
+      <c r="R28" s="49"/>
+      <c r="S28" s="49"/>
+      <c r="T28" s="49"/>
+      <c r="U28" s="49"/>
+      <c r="V28" s="49"/>
+      <c r="W28" s="49"/>
+      <c r="X28" s="49"/>
+      <c r="Y28" s="49"/>
+      <c r="Z28" s="49"/>
+      <c r="AA28" s="49"/>
+    </row>
+    <row r="29" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A29" s="61"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="61" t="s">
+        <v>172</v>
+      </c>
+      <c r="D29" s="61" t="s">
+        <v>199</v>
+      </c>
+      <c r="E29" s="61" t="s">
+        <v>192</v>
+      </c>
+      <c r="F29" s="61" t="s">
+        <v>55</v>
+      </c>
+      <c r="G29" s="61" t="s">
+        <v>211</v>
+      </c>
+      <c r="H29" s="63" t="s">
+        <v>212</v>
+      </c>
+      <c r="I29" s="62"/>
+      <c r="J29" s="62"/>
+      <c r="K29" s="49"/>
+      <c r="L29" s="49"/>
+      <c r="M29" s="49"/>
+      <c r="N29" s="49"/>
+      <c r="O29" s="49"/>
+      <c r="P29" s="49"/>
+      <c r="Q29" s="49"/>
+      <c r="R29" s="49"/>
+      <c r="S29" s="49"/>
+      <c r="T29" s="49"/>
+      <c r="U29" s="49"/>
+      <c r="V29" s="49"/>
+      <c r="W29" s="49"/>
+      <c r="X29" s="49"/>
+      <c r="Y29" s="49"/>
+      <c r="Z29" s="49"/>
+      <c r="AA29" s="49"/>
+    </row>
+    <row r="30" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A30" s="31"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="E30" s="61" t="s">
+        <v>192</v>
+      </c>
+      <c r="F30" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="G30" s="29" t="s">
+        <v>215</v>
+      </c>
+      <c r="H30" s="64" t="s">
+        <v>216</v>
+      </c>
+      <c r="I30" s="67"/>
+      <c r="J30" s="67"/>
+    </row>
+    <row r="31" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A31" s="31"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31" t="s">
+        <v>191</v>
+      </c>
+      <c r="E31" s="61" t="s">
+        <v>192</v>
+      </c>
+      <c r="F31" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="G31" s="31" t="s">
+        <v>217</v>
+      </c>
+      <c r="H31" s="69" t="s">
+        <v>218</v>
+      </c>
+      <c r="I31" s="67"/>
+      <c r="J31" s="67"/>
+    </row>
+    <row r="32" spans="1:27" ht="50.1" customHeight="1">
+      <c r="A32" s="31"/>
+      <c r="B32" s="67"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="61"/>
+      <c r="F32" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="G32" s="29" t="s">
+        <v>219</v>
+      </c>
+      <c r="H32" s="69" t="s">
+        <v>220</v>
+      </c>
+      <c r="I32" s="67"/>
+      <c r="J32" s="67"/>
+    </row>
+    <row r="33" spans="1:10" ht="50.1" customHeight="1">
+      <c r="A33" s="31"/>
+      <c r="B33" s="67"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="67"/>
+      <c r="F33" s="31"/>
+      <c r="G33" s="31" t="s">
+        <v>221</v>
+      </c>
+      <c r="H33" s="64" t="s">
+        <v>222</v>
+      </c>
+      <c r="I33" s="67"/>
+      <c r="J33" s="67"/>
+    </row>
+    <row r="34" spans="1:10" ht="50.1" customHeight="1">
+      <c r="A34" s="31"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
+      <c r="E34" s="67"/>
+      <c r="F34" s="31"/>
+      <c r="G34" s="29" t="s">
+        <v>223</v>
+      </c>
+      <c r="H34" s="69" t="s">
+        <v>224</v>
+      </c>
+      <c r="I34" s="67"/>
+      <c r="J34" s="67"/>
+    </row>
+    <row r="35" spans="1:10" ht="50.1" customHeight="1">
+      <c r="A35" s="31"/>
+      <c r="B35" s="67"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31" t="s">
+        <v>225</v>
+      </c>
+      <c r="H35" s="64" t="s">
+        <v>226</v>
+      </c>
+      <c r="I35" s="67"/>
+      <c r="J35" s="67"/>
+    </row>
+    <row r="36" spans="1:10" ht="50.1" customHeight="1">
+      <c r="A36" s="31"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="67"/>
+      <c r="F36" s="31"/>
+      <c r="G36" s="29" t="s">
+        <v>227</v>
+      </c>
+      <c r="H36" s="69" t="s">
+        <v>228</v>
+      </c>
+      <c r="I36" s="67"/>
+      <c r="J36" s="67"/>
+    </row>
+    <row r="37" spans="1:10" ht="50.1" customHeight="1">
+      <c r="A37" s="31"/>
+      <c r="B37" s="67"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="67"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="64"/>
+      <c r="I37" s="67"/>
+      <c r="J37" s="67"/>
+    </row>
+    <row r="38" spans="1:10" ht="50.1" customHeight="1">
+      <c r="A38" s="31"/>
+      <c r="B38" s="67"/>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="67"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="64"/>
+      <c r="I38" s="67"/>
+      <c r="J38" s="67"/>
+    </row>
+    <row r="39" spans="1:10" ht="50.1" customHeight="1">
+      <c r="A39" s="31"/>
+      <c r="B39" s="67"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="67"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="64"/>
+      <c r="I39" s="67"/>
+      <c r="J39" s="67"/>
+    </row>
+    <row r="40" spans="1:10" ht="50.1" customHeight="1">
+      <c r="A40" s="31"/>
+      <c r="B40" s="67"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="64"/>
+      <c r="I40" s="67"/>
+      <c r="J40" s="67"/>
+    </row>
+    <row r="41" spans="1:10" ht="50.1" customHeight="1">
+      <c r="A41" s="31"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="31"/>
+      <c r="D41" s="31"/>
+      <c r="E41" s="67"/>
+      <c r="F41" s="31"/>
+      <c r="G41" s="31"/>
+      <c r="H41" s="64"/>
+      <c r="I41" s="67"/>
+      <c r="J41" s="67"/>
+    </row>
+    <row r="42" spans="1:10" ht="50.1" customHeight="1">
+      <c r="A42" s="31"/>
+      <c r="B42" s="67"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="67"/>
+      <c r="F42" s="31"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="64"/>
+      <c r="I42" s="67"/>
+      <c r="J42" s="67"/>
+    </row>
+    <row r="43" spans="1:10" ht="50.1" customHeight="1">
+      <c r="A43" s="31"/>
+      <c r="B43" s="67"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="67"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="64"/>
+      <c r="I43" s="67"/>
+      <c r="J43" s="67"/>
+    </row>
+    <row r="44" spans="1:10" ht="50.1" customHeight="1">
+      <c r="A44" s="31"/>
+      <c r="B44" s="67"/>
+      <c r="C44" s="31"/>
+      <c r="D44" s="31"/>
+      <c r="E44" s="67"/>
+      <c r="F44" s="31"/>
+      <c r="G44" s="31"/>
+      <c r="H44" s="64"/>
+      <c r="I44" s="67"/>
+      <c r="J44" s="67"/>
+    </row>
+    <row r="45" spans="1:10" ht="50.1" customHeight="1">
+      <c r="A45" s="31"/>
+      <c r="B45" s="67"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="67"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="31"/>
+      <c r="H45" s="64"/>
+      <c r="I45" s="67"/>
+      <c r="J45" s="67"/>
+    </row>
+    <row r="46" spans="1:10" ht="50.1" customHeight="1">
+      <c r="A46" s="31"/>
+      <c r="B46" s="67"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="64"/>
+      <c r="I46" s="67"/>
+      <c r="J46" s="67"/>
+    </row>
+    <row r="47" spans="1:10" ht="50.1" customHeight="1">
+      <c r="A47" s="31"/>
+      <c r="B47" s="67"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="67"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="64"/>
+      <c r="I47" s="67"/>
+      <c r="J47" s="67"/>
+    </row>
+    <row r="48" spans="1:10" ht="50.1" customHeight="1">
+      <c r="A48" s="31"/>
+      <c r="B48" s="67"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="67"/>
+      <c r="F48" s="31"/>
+      <c r="G48" s="31"/>
+      <c r="H48" s="64"/>
+      <c r="I48" s="67"/>
+      <c r="J48" s="67"/>
+    </row>
+    <row r="49" spans="1:10" ht="50.1" customHeight="1">
+      <c r="A49" s="31"/>
+      <c r="B49" s="67"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="67"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="64"/>
+      <c r="I49" s="67"/>
+      <c r="J49" s="67"/>
+    </row>
+    <row r="50" spans="1:10" ht="50.1" customHeight="1">
+      <c r="A50" s="31"/>
+      <c r="B50" s="67"/>
+      <c r="C50" s="31"/>
+      <c r="D50" s="31"/>
+      <c r="E50" s="67"/>
+      <c r="F50" s="31"/>
+      <c r="G50" s="31"/>
+      <c r="H50" s="64"/>
+      <c r="I50" s="67"/>
+      <c r="J50" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3964,7 +4514,7 @@
       <c r="A1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C1" s="18"/>
+      <c r="C1" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
